--- a/Output/Models/Exposure_models_malf_card_bin.xlsx
+++ b/Output/Models/Exposure_models_malf_card_bin.xlsx
@@ -501,22 +501,22 @@
         </is>
       </c>
       <c r="B3">
-        <v>0.8817591913282654</v>
+        <v>0.8766772755054487</v>
       </c>
       <c r="C3">
-        <v>0.1625546916043608</v>
+        <v>0.1619545478126603</v>
       </c>
       <c r="D3">
-        <v>-0.7741166047968299</v>
+        <v>-0.8126745620437262</v>
       </c>
       <c r="E3">
-        <v>0.4388618388899552</v>
+        <v>0.416404669543169</v>
       </c>
       <c r="F3">
-        <v>0.6411847596429862</v>
+        <v>0.6382396609447357</v>
       </c>
       <c r="G3">
-        <v>1.212597866369735</v>
+        <v>1.204191924159043</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -564,22 +564,22 @@
         </is>
       </c>
       <c r="B4">
-        <v>0.8681244380636584</v>
+        <v>0.9393974313613356</v>
       </c>
       <c r="C4">
-        <v>0.1634830065280434</v>
+        <v>0.1584053488178633</v>
       </c>
       <c r="D4">
-        <v>-0.8650453388154514</v>
+        <v>-0.3946624290099585</v>
       </c>
       <c r="E4">
-        <v>0.3870139044129464</v>
+        <v>0.6930920338625652</v>
       </c>
       <c r="F4">
-        <v>0.6301225103353156</v>
+        <v>0.6886752747759347</v>
       </c>
       <c r="G4">
-        <v>1.196021452339955</v>
+        <v>1.281398601591138</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -627,22 +627,22 @@
         </is>
       </c>
       <c r="B5">
-        <v>1.263316825818303</v>
+        <v>1.205042223761378</v>
       </c>
       <c r="C5">
-        <v>0.157902896801517</v>
+        <v>0.1588661383379912</v>
       </c>
       <c r="D5">
-        <v>1.480281036262924</v>
+        <v>1.174036259368092</v>
       </c>
       <c r="E5">
-        <v>0.138798261944738</v>
+        <v>0.2403805024293082</v>
       </c>
       <c r="F5">
-        <v>0.9270541257145133</v>
+        <v>0.8826228414856498</v>
       </c>
       <c r="G5">
-        <v>1.721549322878598</v>
+        <v>1.645240404841002</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -680,7 +680,7 @@
         </is>
       </c>
       <c r="O5">
-        <v>15313</v>
+        <v>15247</v>
       </c>
     </row>
     <row r="6">
@@ -812,26 +812,26 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_cs</t>
+          <t>pct1_Levo_cs</t>
         </is>
       </c>
       <c r="B8">
-        <v>1.011819308992038</v>
+        <v>1.017086522523065</v>
       </c>
       <c r="C8">
-        <v>0.168761967588946</v>
+        <v>0.2433358028848013</v>
       </c>
       <c r="D8">
-        <v>0.06962473040954903</v>
+        <v>0.06962473040956174</v>
       </c>
       <c r="E8">
-        <v>0.9444923526819202</v>
+        <v>0.94449235268191</v>
       </c>
       <c r="F8">
-        <v>0.7268629221792705</v>
+        <v>0.6312917132823482</v>
       </c>
       <c r="G8">
-        <v>1.408488839930982</v>
+        <v>1.638648144008493</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_cs</t>
+          <t>pct1_Levo_cs</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -875,26 +875,26 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_cs</t>
+          <t>t1_Levo_cs</t>
         </is>
       </c>
       <c r="B9">
-        <v>0.8756656773251953</v>
+        <v>0.820970080466156</v>
       </c>
       <c r="C9">
-        <v>0.1746515092605637</v>
+        <v>0.2524999366150111</v>
       </c>
       <c r="D9">
-        <v>-0.760204754843653</v>
+        <v>-0.7812620297347015</v>
       </c>
       <c r="E9">
-        <v>0.4471322032529947</v>
+        <v>0.4346483974725174</v>
       </c>
       <c r="F9">
-        <v>0.6218343277776218</v>
+        <v>0.5004941368645632</v>
       </c>
       <c r="G9">
-        <v>1.233110402871824</v>
+        <v>1.346652884373335</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_cs</t>
+          <t>t1_Levo_cs</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -938,26 +938,26 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>iqr_t2_Levo_cs</t>
+          <t>t2_Levo_cs</t>
         </is>
       </c>
       <c r="B10">
-        <v>0.8377652850931822</v>
+        <v>0.8698782489456248</v>
       </c>
       <c r="C10">
-        <v>0.1771769190696853</v>
+        <v>0.2541418030769255</v>
       </c>
       <c r="D10">
-        <v>-0.9990991380226039</v>
+        <v>-0.5485206258059502</v>
       </c>
       <c r="E10">
-        <v>0.3177466686855107</v>
+        <v>0.5833344706985819</v>
       </c>
       <c r="F10">
-        <v>0.5919828066218537</v>
+        <v>0.5286065942985895</v>
       </c>
       <c r="G10">
-        <v>1.185593002121746</v>
+        <v>1.431476973897307</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -966,7 +966,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>iqr_t2_Levo_cs</t>
+          <t>t2_Levo_cs</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1001,26 +1001,26 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>iqr_t3_Levo_cs</t>
+          <t>t3_Levo_cs</t>
         </is>
       </c>
       <c r="B11">
-        <v>1.241346755088555</v>
+        <v>1.290021758480755</v>
       </c>
       <c r="C11">
-        <v>0.1689300096576861</v>
+        <v>0.251666698421609</v>
       </c>
       <c r="D11">
-        <v>1.279801519554125</v>
+        <v>1.011890277370176</v>
       </c>
       <c r="E11">
-        <v>0.2006149493290164</v>
+        <v>0.3115905185042577</v>
       </c>
       <c r="F11">
-        <v>0.8914554171107222</v>
+        <v>0.7877310301063295</v>
       </c>
       <c r="G11">
-        <v>1.728568514803801</v>
+        <v>2.112594367558616</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>iqr_t3_Levo_cs</t>
+          <t>t3_Levo_cs</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1058,32 +1058,32 @@
         </is>
       </c>
       <c r="O11">
-        <v>15313</v>
+        <v>15247</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>iqr_w20_Levo_cs</t>
+          <t>w20_Levo_cs</t>
         </is>
       </c>
       <c r="B12">
-        <v>0.8508793578250079</v>
+        <v>0.799438154006876</v>
       </c>
       <c r="C12">
-        <v>0.1439532405621324</v>
+        <v>0.1995441503321374</v>
       </c>
       <c r="D12">
-        <v>-1.121787359671855</v>
+        <v>-1.121787359671842</v>
       </c>
       <c r="E12">
-        <v>0.2619528619456195</v>
+        <v>0.2619528619456248</v>
       </c>
       <c r="F12">
-        <v>0.6417040309279934</v>
+        <v>0.5406703861737368</v>
       </c>
       <c r="G12">
-        <v>1.128239260903035</v>
+        <v>1.182053573536309</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>iqr_w20_Levo_cs</t>
+          <t>w20_Levo_cs</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1127,26 +1127,26 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>iqr_tot_Levo_cs</t>
+          <t>tot_Levo_cs</t>
         </is>
       </c>
       <c r="B13">
-        <v>0.9659443947459975</v>
+        <v>0.8545653978469154</v>
       </c>
       <c r="C13">
-        <v>0.1508615116452888</v>
+        <v>0.6842831817909987</v>
       </c>
       <c r="D13">
-        <v>-0.2296742782387599</v>
+        <v>-0.2296742782387634</v>
       </c>
       <c r="E13">
-        <v>0.8183448836227381</v>
+        <v>0.8183448836227353</v>
       </c>
       <c r="F13">
-        <v>0.718684990990192</v>
+        <v>0.2235025093609873</v>
       </c>
       <c r="G13">
-        <v>1.29827196259612</v>
+        <v>3.26744438478653</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1155,7 +1155,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>iqr_tot_Levo_cs</t>
+          <t>tot_Levo_cs</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1190,26 +1190,26 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_cs</t>
+          <t>pct1_K_cs</t>
         </is>
       </c>
       <c r="B14">
-        <v>0.986601876318469</v>
+        <v>0.9810323797601137</v>
       </c>
       <c r="C14">
-        <v>0.1599144451855685</v>
+        <v>0.2270296151793505</v>
       </c>
       <c r="D14">
-        <v>-0.08434940549636305</v>
+        <v>-0.08434940549636138</v>
       </c>
       <c r="E14">
-        <v>0.9327786324226194</v>
+        <v>0.9327786324226207</v>
       </c>
       <c r="F14">
-        <v>0.7211448635549531</v>
+        <v>0.6286883071356962</v>
       </c>
       <c r="G14">
-        <v>1.34977493642087</v>
+        <v>1.530845284084569</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_cs</t>
+          <t>pct1_K_cs</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1253,26 +1253,26 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>iqr_t1_K_cs</t>
+          <t>t1_K_cs</t>
         </is>
       </c>
       <c r="B15">
-        <v>0.8758670250817698</v>
+        <v>0.8179971847546101</v>
       </c>
       <c r="C15">
-        <v>0.1640190922728812</v>
+        <v>0.2356136140606789</v>
       </c>
       <c r="D15">
-        <v>-0.8080827395359311</v>
+        <v>-0.8526518503886426</v>
       </c>
       <c r="E15">
-        <v>0.4190429531920347</v>
+        <v>0.3938523997106692</v>
       </c>
       <c r="F15">
-        <v>0.6350747877426171</v>
+        <v>0.5154625728076266</v>
       </c>
       <c r="G15">
-        <v>1.207957016137282</v>
+        <v>1.298095011286468</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>iqr_t1_K_cs</t>
+          <t>t1_K_cs</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1316,26 +1316,26 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>iqr_t2_K_cs</t>
+          <t>t2_K_cs</t>
         </is>
       </c>
       <c r="B16">
-        <v>0.8401382621608796</v>
+        <v>0.8847819502257049</v>
       </c>
       <c r="C16">
-        <v>0.1675026994265889</v>
+        <v>0.2362105366190383</v>
       </c>
       <c r="D16">
-        <v>-1.039916392244661</v>
+        <v>-0.5182412690374631</v>
       </c>
       <c r="E16">
-        <v>0.2983787460130122</v>
+        <v>0.6042899443030927</v>
       </c>
       <c r="F16">
-        <v>0.6050234501836773</v>
+        <v>0.5568952082229314</v>
       </c>
       <c r="G16">
-        <v>1.166619739007507</v>
+        <v>1.40572065962511</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>iqr_t2_K_cs</t>
+          <t>t2_K_cs</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1379,26 +1379,26 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>iqr_t3_K_cs</t>
+          <t>t3_K_cs</t>
         </is>
       </c>
       <c r="B17">
-        <v>1.267628664604312</v>
+        <v>1.309890379501877</v>
       </c>
       <c r="C17">
-        <v>0.1577127731891283</v>
+        <v>0.2346085218275022</v>
       </c>
       <c r="D17">
-        <v>1.503669975943642</v>
+        <v>1.150612312968885</v>
       </c>
       <c r="E17">
-        <v>0.1326663636022722</v>
+        <v>0.2498917651657797</v>
       </c>
       <c r="F17">
-        <v>0.9305649599275803</v>
+        <v>0.8270577139213802</v>
       </c>
       <c r="G17">
-        <v>1.726781579495067</v>
+        <v>2.074598637350569</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>iqr_t3_K_cs</t>
+          <t>t3_K_cs</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1436,32 +1436,32 @@
         </is>
       </c>
       <c r="O17">
-        <v>15313</v>
+        <v>15247</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>iqr_w20_K_cs</t>
+          <t>w20_K_cs</t>
         </is>
       </c>
       <c r="B18">
-        <v>0.8641356094030148</v>
+        <v>0.8153410796399484</v>
       </c>
       <c r="C18">
-        <v>0.1315147589746742</v>
+        <v>0.183862143180865</v>
       </c>
       <c r="D18">
         <v>-1.110335967652398</v>
       </c>
       <c r="E18">
-        <v>0.2668542795341083</v>
+        <v>0.2668542795341081</v>
       </c>
       <c r="F18">
-        <v>0.6677845027322311</v>
+        <v>0.5686376143314059</v>
       </c>
       <c r="G18">
-        <v>1.11822054627366</v>
+        <v>1.169076859134749</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>iqr_w20_K_cs</t>
+          <t>w20_K_cs</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1505,26 +1505,26 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>iqr_tot_K_cs</t>
+          <t>tot_K_cs</t>
         </is>
       </c>
       <c r="B19">
-        <v>0.9803936748557696</v>
+        <v>0.9180861656107039</v>
       </c>
       <c r="C19">
-        <v>0.1431379839728326</v>
+        <v>0.6178021437337671</v>
       </c>
       <c r="D19">
-        <v>-0.1383356003410784</v>
+        <v>-0.1383356003410695</v>
       </c>
       <c r="E19">
-        <v>0.889975190971799</v>
+        <v>0.889975190971806</v>
       </c>
       <c r="F19">
-        <v>0.7405616661672785</v>
+        <v>0.2735327331764006</v>
       </c>
       <c r="G19">
-        <v>1.297895640037207</v>
+        <v>3.081467426942984</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>iqr_tot_K_cs</t>
+          <t>tot_K_cs</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1635,22 +1635,22 @@
         </is>
       </c>
       <c r="B21">
-        <v>0.870396334859135</v>
+        <v>0.8637576840987881</v>
       </c>
       <c r="C21">
-        <v>0.1442707988016349</v>
+        <v>0.144559429315609</v>
       </c>
       <c r="D21">
-        <v>-0.9621254953314333</v>
+        <v>-1.01316813732761</v>
       </c>
       <c r="E21">
-        <v>0.3359865686384382</v>
+        <v>0.3109798568791741</v>
       </c>
       <c r="F21">
-        <v>0.6560146332974894</v>
+        <v>0.6506429293873101</v>
       </c>
       <c r="G21">
-        <v>1.15483670833401</v>
+        <v>1.146677083761225</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1698,22 +1698,22 @@
         </is>
       </c>
       <c r="B22">
-        <v>0.8350425351404928</v>
+        <v>0.8902185487787269</v>
       </c>
       <c r="C22">
-        <v>0.1468664753690377</v>
+        <v>0.1448184403356509</v>
       </c>
       <c r="D22">
-        <v>-1.227459259764353</v>
+        <v>-0.8029936360722889</v>
       </c>
       <c r="E22">
-        <v>0.2196500251630009</v>
+        <v>0.4219784128708056</v>
       </c>
       <c r="F22">
-        <v>0.626174860258815</v>
+        <v>0.6702347778137705</v>
       </c>
       <c r="G22">
-        <v>1.11358037466667</v>
+        <v>1.182405167297811</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1761,22 +1761,22 @@
         </is>
       </c>
       <c r="B23">
-        <v>1.118052781065928</v>
+        <v>1.07959682779256</v>
       </c>
       <c r="C23">
-        <v>0.1350843849581012</v>
+        <v>0.1363849796625655</v>
       </c>
       <c r="D23">
-        <v>0.8260657507446085</v>
+        <v>0.5615549749650374</v>
       </c>
       <c r="E23">
-        <v>0.4087667947481198</v>
+        <v>0.5744192644578728</v>
       </c>
       <c r="F23">
-        <v>0.857982182937124</v>
+        <v>0.8263622978854793</v>
       </c>
       <c r="G23">
-        <v>1.456955687552853</v>
+        <v>1.410433793460992</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
         </is>
       </c>
       <c r="O23">
-        <v>15313</v>
+        <v>15247</v>
       </c>
     </row>
     <row r="24">
@@ -1946,26 +1946,26 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_sp</t>
+          <t>pct1_Levo_sp</t>
         </is>
       </c>
       <c r="B26">
-        <v>1.036145580120007</v>
+        <v>1.051506275597432</v>
       </c>
       <c r="C26">
-        <v>0.1611190576824894</v>
+        <v>0.2278943125903988</v>
       </c>
       <c r="D26">
-        <v>0.2203814733476314</v>
+        <v>0.2203814733476384</v>
       </c>
       <c r="E26">
-        <v>0.8255740728661939</v>
+        <v>0.8255740728661883</v>
       </c>
       <c r="F26">
-        <v>0.7555722309941586</v>
+        <v>0.6727099919349288</v>
       </c>
       <c r="G26">
-        <v>1.420906723622729</v>
+        <v>1.643598966681819</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_sp</t>
+          <t>pct1_Levo_sp</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2009,26 +2009,26 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_sp</t>
+          <t>t1_Levo_sp</t>
         </is>
       </c>
       <c r="B27">
-        <v>0.8978491568696243</v>
+        <v>0.8505236525062914</v>
       </c>
       <c r="C27">
-        <v>0.1644160709341078</v>
+        <v>0.2362315100774149</v>
       </c>
       <c r="D27">
-        <v>-0.6553690338013314</v>
+        <v>-0.685357585703794</v>
       </c>
       <c r="E27">
-        <v>0.512230183775565</v>
+        <v>0.4931183017507195</v>
       </c>
       <c r="F27">
-        <v>0.6505072869220685</v>
+        <v>0.5353105093288828</v>
       </c>
       <c r="G27">
-        <v>1.239237629920771</v>
+        <v>1.351347434556357</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_sp</t>
+          <t>t1_Levo_sp</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2072,26 +2072,26 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>iqr_t2_Levo_sp</t>
+          <t>t2_Levo_sp</t>
         </is>
       </c>
       <c r="B28">
-        <v>0.8366679366865033</v>
+        <v>0.8608902339217565</v>
       </c>
       <c r="C28">
-        <v>0.1678708026659012</v>
+        <v>0.2376189566191599</v>
       </c>
       <c r="D28">
-        <v>-1.062293232304871</v>
+        <v>-0.6303717159061288</v>
       </c>
       <c r="E28">
-        <v>0.2881025858126242</v>
+        <v>0.5284514116493159</v>
       </c>
       <c r="F28">
-        <v>0.6020897581596878</v>
+        <v>0.5403636898323668</v>
       </c>
       <c r="G28">
-        <v>1.1626393354022</v>
+        <v>1.371542923418434</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -2100,7 +2100,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>iqr_t2_Levo_sp</t>
+          <t>t2_Levo_sp</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2135,26 +2135,26 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>iqr_t3_Levo_sp</t>
+          <t>t3_Levo_sp</t>
         </is>
       </c>
       <c r="B29">
-        <v>1.19037018932837</v>
+        <v>1.226404493255818</v>
       </c>
       <c r="C29">
-        <v>0.1599827412817982</v>
+        <v>0.2352263927554329</v>
       </c>
       <c r="D29">
-        <v>1.089269635086901</v>
+        <v>0.8676182547156009</v>
       </c>
       <c r="E29">
-        <v>0.276034998996595</v>
+        <v>0.3856033497080643</v>
       </c>
       <c r="F29">
-        <v>0.8699704191886948</v>
+        <v>0.7734080079337463</v>
       </c>
       <c r="G29">
-        <v>1.628769388461608</v>
+        <v>1.944727706009096</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -2163,7 +2163,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>iqr_t3_Levo_sp</t>
+          <t>t3_Levo_sp</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2192,32 +2192,32 @@
         </is>
       </c>
       <c r="O29">
-        <v>15313</v>
+        <v>15247</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>iqr_w20_Levo_sp</t>
+          <t>w20_Levo_sp</t>
         </is>
       </c>
       <c r="B30">
-        <v>0.8304769939771847</v>
+        <v>0.7832222004794579</v>
       </c>
       <c r="C30">
-        <v>0.1449553064761768</v>
+        <v>0.1906715938087947</v>
       </c>
       <c r="D30">
-        <v>-1.281464309519342</v>
+        <v>-1.28146430951934</v>
       </c>
       <c r="E30">
-        <v>0.200030628286172</v>
+        <v>0.2000306282861725</v>
       </c>
       <c r="F30">
-        <v>0.6250883796605607</v>
+        <v>0.5389953694859353</v>
       </c>
       <c r="G30">
-        <v>1.103351237947987</v>
+        <v>1.138111846691646</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>iqr_w20_Levo_sp</t>
+          <t>w20_Levo_sp</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2261,26 +2261,26 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>iqr_tot_Levo_sp</t>
+          <t>tot_Levo_sp</t>
         </is>
       </c>
       <c r="B31">
-        <v>0.9639590602056616</v>
+        <v>0.8525387874731338</v>
       </c>
       <c r="C31">
-        <v>0.1335962674139013</v>
+        <v>0.5806469515669663</v>
       </c>
       <c r="D31">
-        <v>-0.2747565830264914</v>
+        <v>-0.2747565830264787</v>
       </c>
       <c r="E31">
-        <v>0.7835032564291003</v>
+        <v>0.7835032564291101</v>
       </c>
       <c r="F31">
-        <v>0.7418929440056744</v>
+        <v>0.2731911118896584</v>
       </c>
       <c r="G31">
-        <v>1.252494820526929</v>
+        <v>2.660490596193788</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>iqr_tot_Levo_sp</t>
+          <t>tot_Levo_sp</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2324,26 +2324,26 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_sp</t>
+          <t>pct1_K_sp</t>
         </is>
       </c>
       <c r="B32">
-        <v>0.9655001338033725</v>
+        <v>0.9635728872784888</v>
       </c>
       <c r="C32">
-        <v>0.1461833994687381</v>
+        <v>0.1545029117058071</v>
       </c>
       <c r="D32">
-        <v>-0.2401711730376511</v>
+        <v>-0.2401711730376654</v>
       </c>
       <c r="E32">
-        <v>0.8101975603038485</v>
+        <v>0.8101975603038374</v>
       </c>
       <c r="F32">
-        <v>0.7249712815078069</v>
+        <v>0.7118220788935845</v>
       </c>
       <c r="G32">
-        <v>1.285830945517656</v>
+        <v>1.304360649421507</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
@@ -2352,7 +2352,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_sp</t>
+          <t>pct1_K_sp</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2387,26 +2387,26 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>iqr_t1_K_sp</t>
+          <t>t1_K_sp</t>
         </is>
       </c>
       <c r="B33">
-        <v>0.8699030222633113</v>
+        <v>0.8543053279893189</v>
       </c>
       <c r="C33">
-        <v>0.1516204827213438</v>
+        <v>0.1609799182757897</v>
       </c>
       <c r="D33">
-        <v>-0.9192263453323088</v>
+        <v>-0.9781755628782144</v>
       </c>
       <c r="E33">
-        <v>0.3579771938351139</v>
+        <v>0.3279875005207525</v>
       </c>
       <c r="F33">
-        <v>0.64626591442379</v>
+        <v>0.6231416214827153</v>
       </c>
       <c r="G33">
-        <v>1.170928639827066</v>
+        <v>1.171222669566427</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>iqr_t1_K_sp</t>
+          <t>t1_K_sp</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2450,26 +2450,26 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>iqr_t2_K_sp</t>
+          <t>t2_K_sp</t>
         </is>
       </c>
       <c r="B34">
-        <v>0.8125176412490185</v>
+        <v>0.8706564291470866</v>
       </c>
       <c r="C34">
-        <v>0.1549435257157588</v>
+        <v>0.1602123288025097</v>
       </c>
       <c r="D34">
-        <v>-1.339956940752335</v>
+        <v>-0.8645266978642983</v>
       </c>
       <c r="E34">
-        <v>0.1802593443295396</v>
+        <v>0.3872986206573356</v>
       </c>
       <c r="F34">
-        <v>0.5997146125040026</v>
+        <v>0.6360244773972155</v>
       </c>
       <c r="G34">
-        <v>1.100831801620412</v>
+        <v>1.191845038287318</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>iqr_t2_K_sp</t>
+          <t>t2_K_sp</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2513,26 +2513,26 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>iqr_t3_K_sp</t>
+          <t>t3_K_sp</t>
         </is>
       </c>
       <c r="B35">
-        <v>1.156590013349266</v>
+        <v>1.128456771848012</v>
       </c>
       <c r="C35">
-        <v>0.141218368528947</v>
+        <v>0.1565803259855858</v>
       </c>
       <c r="D35">
-        <v>1.030149503428297</v>
+        <v>0.7718147853559688</v>
       </c>
       <c r="E35">
-        <v>0.3029398299554655</v>
+        <v>0.4402241334397778</v>
       </c>
       <c r="F35">
-        <v>0.8769486115444035</v>
+        <v>0.8302397297029176</v>
       </c>
       <c r="G35">
-        <v>1.525403474467468</v>
+        <v>1.533791554862472</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
@@ -2541,7 +2541,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>iqr_t3_K_sp</t>
+          <t>t3_K_sp</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2570,32 +2570,32 @@
         </is>
       </c>
       <c r="O35">
-        <v>15313</v>
+        <v>15247</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>iqr_w20_K_sp</t>
+          <t>w20_K_sp</t>
         </is>
       </c>
       <c r="B36">
-        <v>0.8296531775814551</v>
+        <v>0.8264437345375306</v>
       </c>
       <c r="C36">
-        <v>0.1275747002943382</v>
+        <v>0.1302224941469788</v>
       </c>
       <c r="D36">
-        <v>-1.463828826745045</v>
+        <v>-1.463828826745037</v>
       </c>
       <c r="E36">
-        <v>0.1432407239690517</v>
+        <v>0.1432407239690537</v>
       </c>
       <c r="F36">
-        <v>0.6461075249433587</v>
+        <v>0.640276708313358</v>
       </c>
       <c r="G36">
-        <v>1.065340316430067</v>
+        <v>1.066740734885625</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>iqr_w20_K_sp</t>
+          <t>w20_K_sp</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2639,26 +2639,26 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>iqr_tot_K_sp</t>
+          <t>tot_K_sp</t>
         </is>
       </c>
       <c r="B37">
-        <v>0.9193663741993289</v>
+        <v>0.7903251271441101</v>
       </c>
       <c r="C37">
-        <v>0.1228387984031946</v>
+        <v>0.3438219095863433</v>
       </c>
       <c r="D37">
-        <v>-0.6843975275515569</v>
+        <v>-0.6843975275515479</v>
       </c>
       <c r="E37">
-        <v>0.4937241768457736</v>
+        <v>0.4937241768457793</v>
       </c>
       <c r="F37">
-        <v>0.7226500559318823</v>
+        <v>0.4028506324890831</v>
       </c>
       <c r="G37">
-        <v>1.169631861328041</v>
+        <v>1.550484860197607</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
@@ -2667,7 +2667,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>iqr_tot_K_sp</t>
+          <t>tot_K_sp</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2769,22 +2769,22 @@
         </is>
       </c>
       <c r="B39">
-        <v>0.8900345517223741</v>
+        <v>0.9054104397355863</v>
       </c>
       <c r="C39">
-        <v>0.3736769328755308</v>
+        <v>0.3692200384780758</v>
       </c>
       <c r="D39">
-        <v>-0.3117532408358343</v>
+        <v>-0.2691265456048279</v>
       </c>
       <c r="E39">
-        <v>0.7552280625446961</v>
+        <v>0.7878323033453456</v>
       </c>
       <c r="F39">
-        <v>0.4278903425858686</v>
+        <v>0.4391014095586029</v>
       </c>
       <c r="G39">
-        <v>1.851318958199383</v>
+        <v>1.866921960478882</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -2832,22 +2832,22 @@
         </is>
       </c>
       <c r="B40">
-        <v>1.035454803793655</v>
+        <v>1.36247007623064</v>
       </c>
       <c r="C40">
-        <v>0.386417832204272</v>
+        <v>0.3700799119010811</v>
       </c>
       <c r="D40">
-        <v>0.09016342220900621</v>
+        <v>0.8357635066591439</v>
       </c>
       <c r="E40">
-        <v>0.9281573507476952</v>
+        <v>0.4032879603138628</v>
       </c>
       <c r="F40">
-        <v>0.4855251064855149</v>
+        <v>0.6596512360790749</v>
       </c>
       <c r="G40">
-        <v>2.208262016479974</v>
+        <v>2.814100250395651</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -2895,22 +2895,22 @@
         </is>
       </c>
       <c r="B41">
-        <v>2.158936452655456</v>
+        <v>1.558758128934719</v>
       </c>
       <c r="C41">
-        <v>0.3567821133136154</v>
+        <v>0.3473454502177006</v>
       </c>
       <c r="D41">
-        <v>2.157102861065687</v>
+        <v>1.277948027690022</v>
       </c>
       <c r="E41">
-        <v>0.03099765074522902</v>
+        <v>0.20126775208676</v>
       </c>
       <c r="F41">
-        <v>1.072868202207045</v>
+        <v>0.7890740263072584</v>
       </c>
       <c r="G41">
-        <v>4.344435408763313</v>
+        <v>3.079212879291949</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="O41">
-        <v>15313</v>
+        <v>15247</v>
       </c>
     </row>
     <row r="42">
@@ -3080,26 +3080,26 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_cs</t>
+          <t>pct1_Levo_cs</t>
         </is>
       </c>
       <c r="B44">
-        <v>0.5112500359455429</v>
+        <v>0.3800861263542681</v>
       </c>
       <c r="C44">
-        <v>0.4075617216338413</v>
+        <v>0.5876582275956979</v>
       </c>
       <c r="D44">
-        <v>-1.646122453861699</v>
+        <v>-1.646122453861697</v>
       </c>
       <c r="E44">
-        <v>0.09973855044039667</v>
+        <v>0.09973855044039708</v>
       </c>
       <c r="F44">
-        <v>0.2299938298413637</v>
+        <v>0.1201341354624346</v>
       </c>
       <c r="G44">
-        <v>1.136450484061251</v>
+        <v>1.202534674186475</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_cs</t>
+          <t>pct1_Levo_cs</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3143,26 +3143,26 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_cs</t>
+          <t>t1_Levo_cs</t>
         </is>
       </c>
       <c r="B45">
-        <v>0.8706431075863532</v>
+        <v>0.868891869872339</v>
       </c>
       <c r="C45">
-        <v>0.408563451308408</v>
+        <v>0.5814686052817808</v>
       </c>
       <c r="D45">
-        <v>-0.3390492611232118</v>
+        <v>-0.2416924846998633</v>
       </c>
       <c r="E45">
-        <v>0.7345726205893706</v>
+        <v>0.8090184532926069</v>
       </c>
       <c r="F45">
-        <v>0.3909041904436055</v>
+        <v>0.2779833340695778</v>
       </c>
       <c r="G45">
-        <v>1.939143757777084</v>
+        <v>2.715893325249793</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -3171,7 +3171,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_cs</t>
+          <t>t1_Levo_cs</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3206,26 +3206,26 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>iqr_t2_Levo_cs</t>
+          <t>t2_Levo_cs</t>
         </is>
       </c>
       <c r="B46">
-        <v>0.9864936648869393</v>
+        <v>1.483180889177772</v>
       </c>
       <c r="C46">
-        <v>0.4250452640689976</v>
+        <v>0.587346052183857</v>
       </c>
       <c r="D46">
-        <v>-0.03199276994024066</v>
+        <v>0.6711359162493902</v>
       </c>
       <c r="E46">
-        <v>0.974477816699501</v>
+        <v>0.5021339484364041</v>
       </c>
       <c r="F46">
-        <v>0.4288398307248771</v>
+        <v>0.4690771252684494</v>
       </c>
       <c r="G46">
-        <v>2.269308215183966</v>
+        <v>4.689688393488004</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
@@ -3234,7 +3234,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>iqr_t2_Levo_cs</t>
+          <t>t2_Levo_cs</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3269,26 +3269,26 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>iqr_t3_Levo_cs</t>
+          <t>t3_Levo_cs</t>
         </is>
       </c>
       <c r="B47">
-        <v>2.138849313341631</v>
+        <v>1.906254338493296</v>
       </c>
       <c r="C47">
-        <v>0.3850132386406017</v>
+        <v>0.5535788061827194</v>
       </c>
       <c r="D47">
-        <v>1.974654126329452</v>
+        <v>1.16539909060204</v>
       </c>
       <c r="E47">
-        <v>0.04830741213599528</v>
+        <v>0.2438574852507249</v>
       </c>
       <c r="F47">
-        <v>1.005671923860846</v>
+        <v>0.6441302734168224</v>
       </c>
       <c r="G47">
-        <v>4.548875509638826</v>
+        <v>5.641414094308602</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -3297,7 +3297,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>iqr_t3_Levo_cs</t>
+          <t>t3_Levo_cs</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3326,32 +3326,32 @@
         </is>
       </c>
       <c r="O47">
-        <v>15313</v>
+        <v>15247</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>iqr_w20_Levo_cs</t>
+          <t>w20_Levo_cs</t>
         </is>
       </c>
       <c r="B48">
-        <v>0.8304184755245451</v>
+        <v>0.7729148539533153</v>
       </c>
       <c r="C48">
-        <v>0.2544439586129795</v>
+        <v>0.3527034426617041</v>
       </c>
       <c r="D48">
-        <v>-0.7303200236517414</v>
+        <v>-0.7303200236517885</v>
       </c>
       <c r="E48">
-        <v>0.4651945914533313</v>
+        <v>0.4651945914533025</v>
       </c>
       <c r="F48">
-        <v>0.5043289663422011</v>
+        <v>0.3871773464242473</v>
       </c>
       <c r="G48">
-        <v>1.367351253873053</v>
+        <v>1.54295538460321</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>iqr_w20_Levo_cs</t>
+          <t>w20_Levo_cs</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3395,26 +3395,26 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>iqr_tot_Levo_cs</t>
+          <t>tot_Levo_cs</t>
         </is>
       </c>
       <c r="B49">
-        <v>1.530017434166805</v>
+        <v>6.882601382725079</v>
       </c>
       <c r="C49">
-        <v>0.3210422940752324</v>
+        <v>1.456195421107875</v>
       </c>
       <c r="D49">
-        <v>1.324682566964304</v>
+        <v>1.324682566964191</v>
       </c>
       <c r="E49">
-        <v>0.1852764576215723</v>
+        <v>0.1852764576216097</v>
       </c>
       <c r="F49">
-        <v>0.8155013482176691</v>
+        <v>0.3964941899370921</v>
       </c>
       <c r="G49">
-        <v>2.870569563092298</v>
+        <v>119.4726253138916</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
@@ -3423,7 +3423,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>iqr_tot_Levo_cs</t>
+          <t>tot_Levo_cs</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3458,26 +3458,26 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_cs</t>
+          <t>pct1_K_cs</t>
         </is>
       </c>
       <c r="B50">
-        <v>0.5222342194377285</v>
+        <v>0.3976079236584355</v>
       </c>
       <c r="C50">
-        <v>0.3759488653480328</v>
+        <v>0.5337324350407076</v>
       </c>
       <c r="D50">
-        <v>-1.727998553450336</v>
+        <v>-1.727998553450383</v>
       </c>
       <c r="E50">
-        <v>0.08398848372138049</v>
+        <v>0.08398848372137199</v>
       </c>
       <c r="F50">
-        <v>0.2499522619375136</v>
+        <v>0.1396822294712665</v>
       </c>
       <c r="G50">
-        <v>1.091122672136145</v>
+        <v>1.131797949920987</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
@@ -3486,7 +3486,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_cs</t>
+          <t>pct1_K_cs</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3521,26 +3521,26 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>iqr_t1_K_cs</t>
+          <t>t1_K_cs</t>
         </is>
       </c>
       <c r="B51">
-        <v>0.900892166962254</v>
+        <v>0.8787071876355628</v>
       </c>
       <c r="C51">
-        <v>0.3703531344401604</v>
+        <v>0.5279284729419652</v>
       </c>
       <c r="D51">
-        <v>-0.2818113317736694</v>
+        <v>-0.2449262793909812</v>
       </c>
       <c r="E51">
-        <v>0.7780881814604725</v>
+        <v>0.8065135132870684</v>
       </c>
       <c r="F51">
-        <v>0.435940934950361</v>
+        <v>0.3122271378716136</v>
       </c>
       <c r="G51">
-        <v>1.861735458695478</v>
+        <v>2.472963519013184</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
@@ -3549,7 +3549,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>iqr_t1_K_cs</t>
+          <t>t1_K_cs</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3584,26 +3584,26 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>iqr_t2_K_cs</t>
+          <t>t2_K_cs</t>
         </is>
       </c>
       <c r="B52">
-        <v>0.9363460327931451</v>
+        <v>1.443182840506668</v>
       </c>
       <c r="C52">
-        <v>0.3859030816779975</v>
+        <v>0.5366202662015005</v>
       </c>
       <c r="D52">
-        <v>-0.1704318539856379</v>
+        <v>0.6836323625260823</v>
       </c>
       <c r="E52">
-        <v>0.8646705227296467</v>
+        <v>0.4942073436488379</v>
       </c>
       <c r="F52">
-        <v>0.4394961511289434</v>
+        <v>0.5041379113218388</v>
       </c>
       <c r="G52">
-        <v>1.994884120999354</v>
+        <v>4.131362994843808</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>iqr_t2_K_cs</t>
+          <t>t2_K_cs</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -3647,26 +3647,26 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>iqr_t3_K_cs</t>
+          <t>t3_K_cs</t>
         </is>
       </c>
       <c r="B53">
-        <v>2.202745718673045</v>
+        <v>1.937240004405612</v>
       </c>
       <c r="C53">
-        <v>0.3467650200515556</v>
+        <v>0.4999908538687168</v>
       </c>
       <c r="D53">
-        <v>2.277348032443502</v>
+        <v>1.322552756415054</v>
       </c>
       <c r="E53">
-        <v>0.02276545075936562</v>
+        <v>0.1859841540604084</v>
       </c>
       <c r="F53">
-        <v>1.11634246563747</v>
+        <v>0.7270938015791921</v>
       </c>
       <c r="G53">
-        <v>4.346415952529155</v>
+        <v>5.161505745914003</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
@@ -3675,7 +3675,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>iqr_t3_K_cs</t>
+          <t>t3_K_cs</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -3704,32 +3704,32 @@
         </is>
       </c>
       <c r="O53">
-        <v>15313</v>
+        <v>15247</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>iqr_w20_K_cs</t>
+          <t>w20_K_cs</t>
         </is>
       </c>
       <c r="B54">
-        <v>0.8540118900987588</v>
+        <v>0.8020181671873682</v>
       </c>
       <c r="C54">
-        <v>0.2195291280474578</v>
+        <v>0.3069092494873872</v>
       </c>
       <c r="D54">
-        <v>-0.7188575104443695</v>
+        <v>-0.7188575104443804</v>
       </c>
       <c r="E54">
-        <v>0.4722287185039097</v>
+        <v>0.472228718503903</v>
       </c>
       <c r="F54">
-        <v>0.5553929781892361</v>
+        <v>0.4394835046969411</v>
       </c>
       <c r="G54">
-        <v>1.313189646019528</v>
+        <v>1.463611565904267</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>iqr_w20_K_cs</t>
+          <t>w20_K_cs</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -3773,26 +3773,26 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>iqr_tot_K_cs</t>
+          <t>tot_K_cs</t>
         </is>
       </c>
       <c r="B55">
-        <v>1.568768753818477</v>
+        <v>6.983252782469467</v>
       </c>
       <c r="C55">
-        <v>0.3053433432789556</v>
+        <v>1.317901557761067</v>
       </c>
       <c r="D55">
-        <v>1.474704094139849</v>
+        <v>1.474704094139904</v>
       </c>
       <c r="E55">
-        <v>0.1402921149022701</v>
+        <v>0.1402921149022554</v>
       </c>
       <c r="F55">
-        <v>0.8622837576372491</v>
+        <v>0.5275430711598648</v>
       </c>
       <c r="G55">
-        <v>2.854089945635393</v>
+        <v>92.43950321752924</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
@@ -3801,7 +3801,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>iqr_tot_K_cs</t>
+          <t>tot_K_cs</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -3903,22 +3903,22 @@
         </is>
       </c>
       <c r="B57">
-        <v>0.8491607147687648</v>
+        <v>0.8515814572869187</v>
       </c>
       <c r="C57">
-        <v>0.2608124428757747</v>
+        <v>0.2587988483220131</v>
       </c>
       <c r="D57">
-        <v>-0.6269133860316093</v>
+        <v>-0.6207914803787505</v>
       </c>
       <c r="E57">
-        <v>0.5307160122198252</v>
+        <v>0.5347368295324645</v>
       </c>
       <c r="F57">
-        <v>0.5093143821488967</v>
+        <v>0.5127860680562826</v>
       </c>
       <c r="G57">
-        <v>1.415773724009615</v>
+        <v>1.414217397020459</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
@@ -3966,22 +3966,22 @@
         </is>
       </c>
       <c r="B58">
-        <v>0.838148365802017</v>
+        <v>0.9639257640711882</v>
       </c>
       <c r="C58">
-        <v>0.2667386010154316</v>
+        <v>0.2563582681802757</v>
       </c>
       <c r="D58">
-        <v>-0.6619219940516127</v>
+        <v>-0.1433189411934571</v>
       </c>
       <c r="E58">
-        <v>0.5080212154179278</v>
+        <v>0.8860382973438165</v>
       </c>
       <c r="F58">
-        <v>0.4969041155527067</v>
+        <v>0.5832181552714675</v>
       </c>
       <c r="G58">
-        <v>1.41373891080618</v>
+        <v>1.593148070309533</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
@@ -4029,22 +4029,22 @@
         </is>
       </c>
       <c r="B59">
-        <v>1.172312990412495</v>
+        <v>1.021936097724557</v>
       </c>
       <c r="C59">
-        <v>0.2292557426346786</v>
+        <v>0.235392213445304</v>
       </c>
       <c r="D59">
-        <v>0.6934557465843838</v>
+        <v>0.09218216193620822</v>
       </c>
       <c r="E59">
-        <v>0.488023588309204</v>
+        <v>0.9265533104069182</v>
       </c>
       <c r="F59">
-        <v>0.7479985147443962</v>
+        <v>0.6442545948035449</v>
       </c>
       <c r="G59">
-        <v>1.837326840093412</v>
+        <v>1.621025905373565</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
@@ -4082,7 +4082,7 @@
         </is>
       </c>
       <c r="O59">
-        <v>15313</v>
+        <v>15247</v>
       </c>
     </row>
     <row r="60">
@@ -4214,26 +4214,26 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_sp</t>
+          <t>pct1_Levo_sp</t>
         </is>
       </c>
       <c r="B62">
-        <v>0.6703089354785586</v>
+        <v>0.5679044435318696</v>
       </c>
       <c r="C62">
-        <v>0.3534752987795126</v>
+        <v>0.4999719548496195</v>
       </c>
       <c r="D62">
-        <v>-1.131667690845755</v>
+        <v>-1.131667690845782</v>
       </c>
       <c r="E62">
-        <v>0.2577741697892075</v>
+        <v>0.2577741697891965</v>
       </c>
       <c r="F62">
-        <v>0.3352712309306903</v>
+        <v>0.2131563953106867</v>
       </c>
       <c r="G62">
-        <v>1.340150980849544</v>
+        <v>1.513046120493637</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
@@ -4242,7 +4242,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_sp</t>
+          <t>pct1_Levo_sp</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -4277,26 +4277,26 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_sp</t>
+          <t>t1_Levo_sp</t>
         </is>
       </c>
       <c r="B63">
-        <v>0.9716566147389774</v>
+        <v>0.9911470969613686</v>
       </c>
       <c r="C63">
-        <v>0.3542125735055646</v>
+        <v>0.5007056922851572</v>
       </c>
       <c r="D63">
-        <v>-0.08117389417229591</v>
+        <v>-0.01775958002304679</v>
       </c>
       <c r="E63">
-        <v>0.9353036604208108</v>
+        <v>0.9858306501390092</v>
       </c>
       <c r="F63">
-        <v>0.485295788425976</v>
+        <v>0.3714810422001527</v>
       </c>
       <c r="G63">
-        <v>1.94544564260116</v>
+        <v>2.644475642678018</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
@@ -4305,7 +4305,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_sp</t>
+          <t>t1_Levo_sp</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -4340,26 +4340,26 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>iqr_t2_Levo_sp</t>
+          <t>t2_Levo_sp</t>
         </is>
       </c>
       <c r="B64">
-        <v>0.9265325993758383</v>
+        <v>1.225968432558748</v>
       </c>
       <c r="C64">
-        <v>0.3675480520932959</v>
+        <v>0.5006240622029091</v>
       </c>
       <c r="D64">
-        <v>-0.2076083601320802</v>
+        <v>0.4069542481943094</v>
       </c>
       <c r="E64">
-        <v>0.8355347761522108</v>
+        <v>0.684041591509409</v>
       </c>
       <c r="F64">
-        <v>0.4508200627418779</v>
+        <v>0.4595653888996638</v>
       </c>
       <c r="G64">
-        <v>1.904224609004746</v>
+        <v>3.270478225588703</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
@@ -4368,7 +4368,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>iqr_t2_Levo_sp</t>
+          <t>t2_Levo_sp</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -4403,26 +4403,26 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>iqr_t3_Levo_sp</t>
+          <t>t3_Levo_sp</t>
         </is>
       </c>
       <c r="B65">
-        <v>1.61396053626943</v>
+        <v>1.472490999428706</v>
       </c>
       <c r="C65">
-        <v>0.3288068858318446</v>
+        <v>0.4765414226035606</v>
       </c>
       <c r="D65">
-        <v>1.455842743230404</v>
+        <v>0.8120081607355483</v>
       </c>
       <c r="E65">
-        <v>0.1454360967408968</v>
+        <v>0.4167869488271038</v>
       </c>
       <c r="F65">
-        <v>0.8472507905339853</v>
+        <v>0.5786551924385076</v>
       </c>
       <c r="G65">
-        <v>3.074495346287458</v>
+        <v>3.74701509937451</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>iqr_t3_Levo_sp</t>
+          <t>t3_Levo_sp</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -4460,32 +4460,32 @@
         </is>
       </c>
       <c r="O65">
-        <v>15313</v>
+        <v>15247</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>iqr_w20_Levo_sp</t>
+          <t>w20_Levo_sp</t>
         </is>
       </c>
       <c r="B66">
-        <v>0.777227800340605</v>
+        <v>0.7178426267686503</v>
       </c>
       <c r="C66">
-        <v>0.2523226768836382</v>
+        <v>0.3319006949456642</v>
       </c>
       <c r="D66">
-        <v>-0.9988075402665324</v>
+        <v>-0.9988075402665428</v>
       </c>
       <c r="E66">
-        <v>0.3178879326269103</v>
+        <v>0.3178879326269053</v>
       </c>
       <c r="F66">
-        <v>0.473991850048075</v>
+        <v>0.3745543629034765</v>
       </c>
       <c r="G66">
-        <v>1.274458735020498</v>
+        <v>1.375763007568835</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
@@ -4494,7 +4494,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>iqr_w20_Levo_sp</t>
+          <t>w20_Levo_sp</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -4529,26 +4529,26 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>iqr_tot_Levo_sp</t>
+          <t>tot_Levo_sp</t>
         </is>
       </c>
       <c r="B67">
-        <v>1.201880267885814</v>
+        <v>2.223818086480823</v>
       </c>
       <c r="C67">
-        <v>0.2196713665566203</v>
+        <v>0.9547535406994357</v>
       </c>
       <c r="D67">
-        <v>0.837101454277267</v>
+        <v>0.8371014542771726</v>
       </c>
       <c r="E67">
-        <v>0.402535543030382</v>
+        <v>0.4025355430304351</v>
       </c>
       <c r="F67">
-        <v>0.7814057432197729</v>
+        <v>0.3423036821267962</v>
       </c>
       <c r="G67">
-        <v>1.84861218498493</v>
+        <v>14.4473084573112</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
@@ -4557,7 +4557,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>iqr_tot_Levo_sp</t>
+          <t>tot_Levo_sp</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -4592,26 +4592,26 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_sp</t>
+          <t>pct1_K_sp</t>
         </is>
       </c>
       <c r="B68">
-        <v>0.6127519670067392</v>
+        <v>0.5959073942154985</v>
       </c>
       <c r="C68">
-        <v>0.2922909667901296</v>
+        <v>0.3089256755452457</v>
       </c>
       <c r="D68">
-        <v>-1.675710514863199</v>
+        <v>-1.675710514863198</v>
       </c>
       <c r="E68">
-        <v>0.0937949092251493</v>
+        <v>0.09379490922514956</v>
       </c>
       <c r="F68">
-        <v>0.3455303436294128</v>
+        <v>0.3252525892600996</v>
       </c>
       <c r="G68">
-        <v>1.086633865861924</v>
+        <v>1.091784152398347</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
@@ -4620,7 +4620,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_sp</t>
+          <t>pct1_K_sp</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -4655,26 +4655,26 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>iqr_t1_K_sp</t>
+          <t>t1_K_sp</t>
         </is>
       </c>
       <c r="B69">
-        <v>0.861980102814157</v>
+        <v>0.8551002514576845</v>
       </c>
       <c r="C69">
-        <v>0.2894173628603031</v>
+        <v>0.3044574592091816</v>
       </c>
       <c r="D69">
-        <v>-0.5131796161059101</v>
+        <v>-0.5141492153245589</v>
       </c>
       <c r="E69">
-        <v>0.6078256833027478</v>
+        <v>0.6071476707094192</v>
       </c>
       <c r="F69">
-        <v>0.4888152372337585</v>
+        <v>0.4708281005221451</v>
       </c>
       <c r="G69">
-        <v>1.520021556308784</v>
+        <v>1.553000849422758</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
@@ -4683,7 +4683,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>iqr_t1_K_sp</t>
+          <t>t1_K_sp</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -4718,26 +4718,26 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>iqr_t2_K_sp</t>
+          <t>t2_K_sp</t>
         </is>
       </c>
       <c r="B70">
-        <v>0.7775199057571345</v>
+        <v>0.9403414387704774</v>
       </c>
       <c r="C70">
-        <v>0.2980899994381404</v>
+        <v>0.2993601868753127</v>
       </c>
       <c r="D70">
-        <v>-0.8441948185810295</v>
+        <v>-0.2054790170283969</v>
       </c>
       <c r="E70">
-        <v>0.3985605494634731</v>
+        <v>0.837197890319027</v>
       </c>
       <c r="F70">
-        <v>0.4334877697133605</v>
+        <v>0.522961505112577</v>
       </c>
       <c r="G70">
-        <v>1.394588835224412</v>
+        <v>1.690835774381868</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
@@ -4746,7 +4746,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>iqr_t2_K_sp</t>
+          <t>t2_K_sp</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -4781,26 +4781,26 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>iqr_t3_K_sp</t>
+          <t>t3_K_sp</t>
         </is>
       </c>
       <c r="B71">
-        <v>1.306873340423066</v>
+        <v>1.136921118909979</v>
       </c>
       <c r="C71">
-        <v>0.2489957036526148</v>
+        <v>0.2816574076229513</v>
       </c>
       <c r="D71">
-        <v>1.074868029415592</v>
+        <v>0.4556025596356689</v>
       </c>
       <c r="E71">
-        <v>0.2824338174100257</v>
+        <v>0.6486758021863005</v>
       </c>
       <c r="F71">
-        <v>0.8022098153780566</v>
+        <v>0.6546107210274339</v>
       </c>
       <c r="G71">
-        <v>2.129016493152299</v>
+        <v>1.974592821508872</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
@@ -4809,7 +4809,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>iqr_t3_K_sp</t>
+          <t>t3_K_sp</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -4838,32 +4838,32 @@
         </is>
       </c>
       <c r="O71">
-        <v>15313</v>
+        <v>15247</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>iqr_w20_K_sp</t>
+          <t>w20_K_sp</t>
         </is>
       </c>
       <c r="B72">
-        <v>0.7685359489303988</v>
+        <v>0.76434805375918</v>
       </c>
       <c r="C72">
-        <v>0.204409353542483</v>
+        <v>0.2086518391488242</v>
       </c>
       <c r="D72">
-        <v>-1.287944678099894</v>
+        <v>-1.287944678099876</v>
       </c>
       <c r="E72">
-        <v>0.1977652214627668</v>
+        <v>0.197765221462773</v>
       </c>
       <c r="F72">
-        <v>0.5148380416067823</v>
+        <v>0.5077926338377392</v>
       </c>
       <c r="G72">
-        <v>1.147249148402028</v>
+        <v>1.150524659780968</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
@@ -4872,7 +4872,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>iqr_w20_K_sp</t>
+          <t>w20_K_sp</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -4907,26 +4907,26 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>iqr_tot_K_sp</t>
+          <t>tot_K_sp</t>
         </is>
       </c>
       <c r="B73">
-        <v>0.985882120970437</v>
+        <v>0.960984415016795</v>
       </c>
       <c r="C73">
-        <v>0.1698839964861294</v>
+        <v>0.4754999303094917</v>
       </c>
       <c r="D73">
-        <v>-0.08369525434365332</v>
+        <v>-0.08369525434369525</v>
       </c>
       <c r="E73">
-        <v>0.9332987303932004</v>
+        <v>0.9332987303931671</v>
       </c>
       <c r="F73">
-        <v>0.7066745821032854</v>
+        <v>0.3784165047068712</v>
       </c>
       <c r="G73">
-        <v>1.375404721019254</v>
+        <v>2.440409005470113</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
@@ -4935,7 +4935,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>iqr_tot_K_sp</t>
+          <t>tot_K_sp</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -4970,37 +4970,37 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
+          <t>iqr_pct1_PM25_cs</t>
+        </is>
+      </c>
+      <c r="B74">
+        <v>0.7256489362916529</v>
+      </c>
+      <c r="C74">
+        <v>0.3318963011070314</v>
+      </c>
+      <c r="D74">
+        <v>-0.9662323408452851</v>
+      </c>
+      <c r="E74">
+        <v>0.3339279332637771</v>
+      </c>
+      <c r="F74">
+        <v>0.3786307827559006</v>
+      </c>
+      <c r="G74">
+        <v>1.39071201477213</v>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>malf_card_bin</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
           <t>iqr_pct1_PM25_cs + iqr_t1_PM25_cs + iqr_t2_PM25_cs + iqr_t3_PM25_cs</t>
         </is>
       </c>
-      <c r="B74">
-        <v>0.7323682239670715</v>
-      </c>
-      <c r="C74">
-        <v>0.3182988383633297</v>
-      </c>
-      <c r="D74">
-        <v>-0.9785516494414928</v>
-      </c>
-      <c r="E74">
-        <v>0.3278015593546217</v>
-      </c>
-      <c r="F74">
-        <v>0.3924578591256098</v>
-      </c>
-      <c r="G74">
-        <v>1.366677218980127</v>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>malf_card_bin</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>iqr_pct1_PM25_cs + iqr_t1_PM25_cs + iqr_t2_PM25_cs + iqr_t3_PM25_cs</t>
-        </is>
-      </c>
       <c r="J74" t="inlineStr">
         <is>
           <t>pct1_t1_t2_t3</t>
@@ -5027,43 +5027,43 @@
         </is>
       </c>
       <c r="O74">
-        <v>15307</v>
+        <v>15241</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
+          <t>iqr_t1_PM25_cs</t>
+        </is>
+      </c>
+      <c r="B75">
+        <v>1.230233869533664</v>
+      </c>
+      <c r="C75">
+        <v>0.3104587747463876</v>
+      </c>
+      <c r="D75">
+        <v>0.6674132155289564</v>
+      </c>
+      <c r="E75">
+        <v>0.5045082267213583</v>
+      </c>
+      <c r="F75">
+        <v>0.6694600894868951</v>
+      </c>
+      <c r="G75">
+        <v>2.260740255491211</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>malf_card_bin</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
           <t>iqr_pct1_PM25_cs + iqr_t1_PM25_cs + iqr_t2_PM25_cs + iqr_t3_PM25_cs</t>
         </is>
       </c>
-      <c r="B75">
-        <v>1.602160397953861</v>
-      </c>
-      <c r="C75">
-        <v>0.3138705605540006</v>
-      </c>
-      <c r="D75">
-        <v>1.501743159246525</v>
-      </c>
-      <c r="E75">
-        <v>0.1331634529918723</v>
-      </c>
-      <c r="F75">
-        <v>0.8660418661602088</v>
-      </c>
-      <c r="G75">
-        <v>2.963965185831815</v>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>malf_card_bin</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>iqr_pct1_PM25_cs + iqr_t1_PM25_cs + iqr_t2_PM25_cs + iqr_t3_PM25_cs</t>
-        </is>
-      </c>
       <c r="J75" t="inlineStr">
         <is>
           <t>pct1_t1_t2_t3</t>
@@ -5090,43 +5090,43 @@
         </is>
       </c>
       <c r="O75">
-        <v>15307</v>
+        <v>15241</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
+          <t>iqr_t2_PM25_cs</t>
+        </is>
+      </c>
+      <c r="B76">
+        <v>0.7078841880800792</v>
+      </c>
+      <c r="C76">
+        <v>0.3188702788468946</v>
+      </c>
+      <c r="D76">
+        <v>-1.083433602140185</v>
+      </c>
+      <c r="E76">
+        <v>0.2786160076138682</v>
+      </c>
+      <c r="F76">
+        <v>0.3789128539651284</v>
+      </c>
+      <c r="G76">
+        <v>1.322467734968711</v>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>malf_card_bin</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
           <t>iqr_pct1_PM25_cs + iqr_t1_PM25_cs + iqr_t2_PM25_cs + iqr_t3_PM25_cs</t>
         </is>
       </c>
-      <c r="B76">
-        <v>0.5842705491784366</v>
-      </c>
-      <c r="C76">
-        <v>0.3293503379235137</v>
-      </c>
-      <c r="D76">
-        <v>-1.631670207709245</v>
-      </c>
-      <c r="E76">
-        <v>0.1027489793813554</v>
-      </c>
-      <c r="F76">
-        <v>0.3063871027313587</v>
-      </c>
-      <c r="G76">
-        <v>1.114185524109963</v>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>malf_card_bin</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>iqr_pct1_PM25_cs + iqr_t1_PM25_cs + iqr_t2_PM25_cs + iqr_t3_PM25_cs</t>
-        </is>
-      </c>
       <c r="J76" t="inlineStr">
         <is>
           <t>pct1_t1_t2_t3</t>
@@ -5153,43 +5153,43 @@
         </is>
       </c>
       <c r="O76">
-        <v>15307</v>
+        <v>15241</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
+          <t>iqr_t3_PM25_cs</t>
+        </is>
+      </c>
+      <c r="B77">
+        <v>1.437987809869159</v>
+      </c>
+      <c r="C77">
+        <v>0.3012475818177799</v>
+      </c>
+      <c r="D77">
+        <v>1.205801487031342</v>
+      </c>
+      <c r="E77">
+        <v>0.2278940420114172</v>
+      </c>
+      <c r="F77">
+        <v>0.7967696775877248</v>
+      </c>
+      <c r="G77">
+        <v>2.595240506130622</v>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>malf_card_bin</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
           <t>iqr_pct1_PM25_cs + iqr_t1_PM25_cs + iqr_t2_PM25_cs + iqr_t3_PM25_cs</t>
         </is>
       </c>
-      <c r="B77">
-        <v>1.782257282246268</v>
-      </c>
-      <c r="C77">
-        <v>0.2930283095233923</v>
-      </c>
-      <c r="D77">
-        <v>1.972098524991974</v>
-      </c>
-      <c r="E77">
-        <v>0.04859836032471869</v>
-      </c>
-      <c r="F77">
-        <v>1.003562093103362</v>
-      </c>
-      <c r="G77">
-        <v>3.165166402705783</v>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>malf_card_bin</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>iqr_pct1_PM25_cs + iqr_t1_PM25_cs + iqr_t2_PM25_cs + iqr_t3_PM25_cs</t>
-        </is>
-      </c>
       <c r="J77" t="inlineStr">
         <is>
           <t>pct1_t1_t2_t3</t>
@@ -5216,32 +5216,32 @@
         </is>
       </c>
       <c r="O77">
-        <v>15307</v>
+        <v>15241</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_cs + iqr_t1_Levo_cs + iqr_t2_Levo_cs + iqr_t3_Levo_cs</t>
+          <t>pct1_Levo_cs</t>
         </is>
       </c>
       <c r="B78">
-        <v>0.6955305355181872</v>
+        <v>0.5570913028334833</v>
       </c>
       <c r="C78">
-        <v>0.39524370894885</v>
+        <v>0.5702063363569571</v>
       </c>
       <c r="D78">
-        <v>-0.9186240184228041</v>
+        <v>-1.025990235946369</v>
       </c>
       <c r="E78">
-        <v>0.3582922645914908</v>
+        <v>0.304896186490453</v>
       </c>
       <c r="F78">
-        <v>0.3205414124914723</v>
+        <v>0.1822073387197929</v>
       </c>
       <c r="G78">
-        <v>1.509205072998443</v>
+        <v>1.703283313796597</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
@@ -5250,7 +5250,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_cs + iqr_t1_Levo_cs + iqr_t2_Levo_cs + iqr_t3_Levo_cs</t>
+          <t>pct1_Levo_cs + t1_Levo_cs + t2_Levo_cs + t3_Levo_cs</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -5279,32 +5279,32 @@
         </is>
       </c>
       <c r="O78">
-        <v>15307</v>
+        <v>15241</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_cs + iqr_t1_Levo_cs + iqr_t2_Levo_cs + iqr_t3_Levo_cs</t>
+          <t>t1_Levo_cs</t>
         </is>
       </c>
       <c r="B79">
-        <v>1.458488429062184</v>
+        <v>1.147896649674967</v>
       </c>
       <c r="C79">
-        <v>0.3610316032034531</v>
+        <v>0.5431988197398864</v>
       </c>
       <c r="D79">
-        <v>1.045339448111449</v>
+        <v>0.2539240926467189</v>
       </c>
       <c r="E79">
-        <v>0.295866111690343</v>
+        <v>0.7995542014297413</v>
       </c>
       <c r="F79">
-        <v>0.7187739521351676</v>
+        <v>0.3958504242164708</v>
       </c>
       <c r="G79">
-        <v>2.959467982095505</v>
+        <v>3.328698512684798</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
@@ -5313,7 +5313,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_cs + iqr_t1_Levo_cs + iqr_t2_Levo_cs + iqr_t3_Levo_cs</t>
+          <t>pct1_Levo_cs + t1_Levo_cs + t2_Levo_cs + t3_Levo_cs</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -5342,32 +5342,32 @@
         </is>
       </c>
       <c r="O79">
-        <v>15307</v>
+        <v>15241</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_cs + iqr_t1_Levo_cs + iqr_t2_Levo_cs + iqr_t3_Levo_cs</t>
+          <t>t2_Levo_cs</t>
         </is>
       </c>
       <c r="B80">
-        <v>0.555742238422927</v>
+        <v>0.5046109715143772</v>
       </c>
       <c r="C80">
-        <v>0.3871343819198242</v>
+        <v>0.5903975520396781</v>
       </c>
       <c r="D80">
-        <v>-1.517433531149568</v>
+        <v>-1.158486341373536</v>
       </c>
       <c r="E80">
-        <v>0.129157263456251</v>
+        <v>0.2466656224013585</v>
       </c>
       <c r="F80">
-        <v>0.2602220073398191</v>
+        <v>0.1586387873912312</v>
       </c>
       <c r="G80">
-        <v>1.186869007447186</v>
+        <v>1.605107028111074</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
@@ -5376,7 +5376,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_cs + iqr_t1_Levo_cs + iqr_t2_Levo_cs + iqr_t3_Levo_cs</t>
+          <t>pct1_Levo_cs + t1_Levo_cs + t2_Levo_cs + t3_Levo_cs</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -5405,32 +5405,32 @@
         </is>
       </c>
       <c r="O80">
-        <v>15307</v>
+        <v>15241</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_cs + iqr_t1_Levo_cs + iqr_t2_Levo_cs + iqr_t3_Levo_cs</t>
+          <t>t3_Levo_cs</t>
         </is>
       </c>
       <c r="B81">
-        <v>1.590683647124594</v>
+        <v>1.43743023816038</v>
       </c>
       <c r="C81">
-        <v>0.3682575818857317</v>
+        <v>0.5386750291638097</v>
       </c>
       <c r="D81">
-        <v>1.260432679189161</v>
+        <v>0.6736101413492835</v>
       </c>
       <c r="E81">
-        <v>0.2075133190895027</v>
+        <v>0.5005592039650374</v>
       </c>
       <c r="F81">
-        <v>0.7728983752943547</v>
+        <v>0.500110255436564</v>
       </c>
       <c r="G81">
-        <v>3.27374794165657</v>
+        <v>4.131500338408664</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
@@ -5439,7 +5439,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_cs + iqr_t1_Levo_cs + iqr_t2_Levo_cs + iqr_t3_Levo_cs</t>
+          <t>pct1_Levo_cs + t1_Levo_cs + t2_Levo_cs + t3_Levo_cs</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -5468,32 +5468,32 @@
         </is>
       </c>
       <c r="O81">
-        <v>15307</v>
+        <v>15241</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_cs + iqr_t1_K_cs + iqr_t2_K_cs + iqr_t3_K_cs</t>
+          <t>pct1_K_cs</t>
         </is>
       </c>
       <c r="B82">
-        <v>0.6833953133549453</v>
+        <v>0.56172363402814</v>
       </c>
       <c r="C82">
-        <v>0.3339047308044649</v>
+        <v>0.4761969323928021</v>
       </c>
       <c r="D82">
-        <v>-1.140091056042238</v>
+        <v>-1.21114871853454</v>
       </c>
       <c r="E82">
-        <v>0.254248367728642</v>
+        <v>0.2258384125469573</v>
       </c>
       <c r="F82">
-        <v>0.3551826752084428</v>
+        <v>0.2208935999747077</v>
       </c>
       <c r="G82">
-        <v>1.314898464688411</v>
+        <v>1.428440846914118</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_cs + iqr_t1_K_cs + iqr_t2_K_cs + iqr_t3_K_cs</t>
+          <t>pct1_K_cs + t1_K_cs + t2_K_cs + t3_K_cs</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -5531,32 +5531,32 @@
         </is>
       </c>
       <c r="O82">
-        <v>15307</v>
+        <v>15241</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_cs + iqr_t1_K_cs + iqr_t2_K_cs + iqr_t3_K_cs</t>
+          <t>t1_K_cs</t>
         </is>
       </c>
       <c r="B83">
-        <v>1.477820733363263</v>
+        <v>1.176702051193079</v>
       </c>
       <c r="C83">
-        <v>0.308110265156204</v>
+        <v>0.4534918428341207</v>
       </c>
       <c r="D83">
-        <v>1.267625812338481</v>
+        <v>0.3588061312051939</v>
       </c>
       <c r="E83">
-        <v>0.2049316095010624</v>
+        <v>0.7197401256465331</v>
       </c>
       <c r="F83">
-        <v>0.8079003980376321</v>
+        <v>0.4837862869941661</v>
       </c>
       <c r="G83">
-        <v>2.703246743364773</v>
+        <v>2.86206483008208</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
@@ -5565,7 +5565,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_cs + iqr_t1_K_cs + iqr_t2_K_cs + iqr_t3_K_cs</t>
+          <t>pct1_K_cs + t1_K_cs + t2_K_cs + t3_K_cs</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -5594,32 +5594,32 @@
         </is>
       </c>
       <c r="O83">
-        <v>15307</v>
+        <v>15241</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_cs + iqr_t1_K_cs + iqr_t2_K_cs + iqr_t3_K_cs</t>
+          <t>t2_K_cs</t>
         </is>
       </c>
       <c r="B84">
-        <v>0.5514720148554125</v>
+        <v>0.5248354202411012</v>
       </c>
       <c r="C84">
-        <v>0.3322072526228817</v>
+        <v>0.4886441389148964</v>
       </c>
       <c r="D84">
-        <v>-1.791544828014027</v>
+        <v>-1.319304785326833</v>
       </c>
       <c r="E84">
-        <v>0.07320590766090657</v>
+        <v>0.1870672386663001</v>
       </c>
       <c r="F84">
-        <v>0.2875730293677023</v>
+        <v>0.2014134608930577</v>
       </c>
       <c r="G84">
-        <v>1.057544874209419</v>
+        <v>1.367595875262315</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
@@ -5628,7 +5628,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_cs + iqr_t1_K_cs + iqr_t2_K_cs + iqr_t3_K_cs</t>
+          <t>pct1_K_cs + t1_K_cs + t2_K_cs + t3_K_cs</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -5657,32 +5657,32 @@
         </is>
       </c>
       <c r="O84">
-        <v>15307</v>
+        <v>15241</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_cs + iqr_t1_K_cs + iqr_t2_K_cs + iqr_t3_K_cs</t>
+          <t>t3_K_cs</t>
         </is>
       </c>
       <c r="B85">
-        <v>1.624838131031089</v>
+        <v>1.490976186923029</v>
       </c>
       <c r="C85">
-        <v>0.3076782748176368</v>
+        <v>0.4520710005750315</v>
       </c>
       <c r="D85">
-        <v>1.577648598799046</v>
+        <v>0.8835582550861865</v>
       </c>
       <c r="E85">
-        <v>0.1146463609766969</v>
+        <v>0.3769347221757902</v>
       </c>
       <c r="F85">
-        <v>0.8890248080219948</v>
+        <v>0.6147056060466985</v>
       </c>
       <c r="G85">
-        <v>2.969657233667751</v>
+        <v>3.616381513531625</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
@@ -5691,7 +5691,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_cs + iqr_t1_K_cs + iqr_t2_K_cs + iqr_t3_K_cs</t>
+          <t>pct1_K_cs + t1_K_cs + t2_K_cs + t3_K_cs</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -5720,43 +5720,43 @@
         </is>
       </c>
       <c r="O85">
-        <v>15307</v>
+        <v>15241</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
+          <t>iqr_pct1_PM25_sp</t>
+        </is>
+      </c>
+      <c r="B86">
+        <v>0.7303641039006238</v>
+      </c>
+      <c r="C86">
+        <v>0.2692243884542612</v>
+      </c>
+      <c r="D86">
+        <v>-1.167101162427251</v>
+      </c>
+      <c r="E86">
+        <v>0.2431695184921446</v>
+      </c>
+      <c r="F86">
+        <v>0.4308987213110758</v>
+      </c>
+      <c r="G86">
+        <v>1.237951513626016</v>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>malf_card_bin</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
           <t>iqr_pct1_PM25_sp + iqr_t1_PM25_sp + iqr_t2_PM25_sp + iqr_t3_PM25_sp</t>
         </is>
       </c>
-      <c r="B86">
-        <v>0.6506992507444492</v>
-      </c>
-      <c r="C86">
-        <v>0.2442948226621508</v>
-      </c>
-      <c r="D86">
-        <v>-1.758971881843528</v>
-      </c>
-      <c r="E86">
-        <v>0.07858228458716589</v>
-      </c>
-      <c r="F86">
-        <v>0.4031216998153818</v>
-      </c>
-      <c r="G86">
-        <v>1.050326775049066</v>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>malf_card_bin</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>iqr_pct1_PM25_sp + iqr_t1_PM25_sp + iqr_t2_PM25_sp + iqr_t3_PM25_sp</t>
-        </is>
-      </c>
       <c r="J86" t="inlineStr">
         <is>
           <t>pct1_t1_t2_t3</t>
@@ -5783,43 +5783,43 @@
         </is>
       </c>
       <c r="O86">
-        <v>15307</v>
+        <v>15241</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
+          <t>iqr_t1_PM25_sp</t>
+        </is>
+      </c>
+      <c r="B87">
+        <v>1.119979205961717</v>
+      </c>
+      <c r="C87">
+        <v>0.2615543360823582</v>
+      </c>
+      <c r="D87">
+        <v>0.4332182778012217</v>
+      </c>
+      <c r="E87">
+        <v>0.6648562015197294</v>
+      </c>
+      <c r="F87">
+        <v>0.6707713503013801</v>
+      </c>
+      <c r="G87">
+        <v>1.870016394145416</v>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>malf_card_bin</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
           <t>iqr_pct1_PM25_sp + iqr_t1_PM25_sp + iqr_t2_PM25_sp + iqr_t3_PM25_sp</t>
         </is>
       </c>
-      <c r="B87">
-        <v>1.422836310327939</v>
-      </c>
-      <c r="C87">
-        <v>0.2692258826598947</v>
-      </c>
-      <c r="D87">
-        <v>1.309875104184236</v>
-      </c>
-      <c r="E87">
-        <v>0.190238090492384</v>
-      </c>
-      <c r="F87">
-        <v>0.8394396000164241</v>
-      </c>
-      <c r="G87">
-        <v>2.411684135401777</v>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>malf_card_bin</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>iqr_pct1_PM25_sp + iqr_t1_PM25_sp + iqr_t2_PM25_sp + iqr_t3_PM25_sp</t>
-        </is>
-      </c>
       <c r="J87" t="inlineStr">
         <is>
           <t>pct1_t1_t2_t3</t>
@@ -5846,43 +5846,43 @@
         </is>
       </c>
       <c r="O87">
-        <v>15307</v>
+        <v>15241</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
+          <t>iqr_t2_PM25_sp</t>
+        </is>
+      </c>
+      <c r="B88">
+        <v>0.6864739587343537</v>
+      </c>
+      <c r="C88">
+        <v>0.2670051230099925</v>
+      </c>
+      <c r="D88">
+        <v>-1.408912996249604</v>
+      </c>
+      <c r="E88">
+        <v>0.1588608961537128</v>
+      </c>
+      <c r="F88">
+        <v>0.4067699801408931</v>
+      </c>
+      <c r="G88">
+        <v>1.158508540520098</v>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>malf_card_bin</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
           <t>iqr_pct1_PM25_sp + iqr_t1_PM25_sp + iqr_t2_PM25_sp + iqr_t3_PM25_sp</t>
         </is>
       </c>
-      <c r="B88">
-        <v>0.530489383124735</v>
-      </c>
-      <c r="C88">
-        <v>0.2873288897874641</v>
-      </c>
-      <c r="D88">
-        <v>-2.206375191012873</v>
-      </c>
-      <c r="E88">
-        <v>0.0273577406216228</v>
-      </c>
-      <c r="F88">
-        <v>0.3020660400685506</v>
-      </c>
-      <c r="G88">
-        <v>0.9316472170926494</v>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>malf_card_bin</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>iqr_pct1_PM25_sp + iqr_t1_PM25_sp + iqr_t2_PM25_sp + iqr_t3_PM25_sp</t>
-        </is>
-      </c>
       <c r="J88" t="inlineStr">
         <is>
           <t>pct1_t1_t2_t3</t>
@@ -5909,43 +5909,43 @@
         </is>
       </c>
       <c r="O88">
-        <v>15307</v>
+        <v>15241</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
+          <t>iqr_t3_PM25_sp</t>
+        </is>
+      </c>
+      <c r="B89">
+        <v>1.267977342237366</v>
+      </c>
+      <c r="C89">
+        <v>0.2479838014624595</v>
+      </c>
+      <c r="D89">
+        <v>0.9574132889214084</v>
+      </c>
+      <c r="E89">
+        <v>0.3383586936480674</v>
+      </c>
+      <c r="F89">
+        <v>0.7798791301453665</v>
+      </c>
+      <c r="G89">
+        <v>2.061558616304621</v>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>malf_card_bin</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
           <t>iqr_pct1_PM25_sp + iqr_t1_PM25_sp + iqr_t2_PM25_sp + iqr_t3_PM25_sp</t>
         </is>
       </c>
-      <c r="B89">
-        <v>1.485792707373373</v>
-      </c>
-      <c r="C89">
-        <v>0.2232127129114348</v>
-      </c>
-      <c r="D89">
-        <v>1.77386150790211</v>
-      </c>
-      <c r="E89">
-        <v>0.07608606107279511</v>
-      </c>
-      <c r="F89">
-        <v>0.9593105412955975</v>
-      </c>
-      <c r="G89">
-        <v>2.301215168867475</v>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>malf_card_bin</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>iqr_pct1_PM25_sp + iqr_t1_PM25_sp + iqr_t2_PM25_sp + iqr_t3_PM25_sp</t>
-        </is>
-      </c>
       <c r="J89" t="inlineStr">
         <is>
           <t>pct1_t1_t2_t3</t>
@@ -5972,32 +5972,32 @@
         </is>
       </c>
       <c r="O89">
-        <v>15307</v>
+        <v>15241</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_sp + iqr_t1_Levo_sp + iqr_t2_Levo_sp + iqr_t3_Levo_sp</t>
+          <t>pct1_Levo_sp</t>
         </is>
       </c>
       <c r="B90">
-        <v>0.7247007749349396</v>
+        <v>0.6902595906726272</v>
       </c>
       <c r="C90">
-        <v>0.3112341040296678</v>
+        <v>0.4643652112518663</v>
       </c>
       <c r="D90">
-        <v>-1.034579531549422</v>
+        <v>-0.7982672362078251</v>
       </c>
       <c r="E90">
-        <v>0.3008653170441813</v>
+        <v>0.4247154268848139</v>
       </c>
       <c r="F90">
-        <v>0.3937637896162287</v>
+        <v>0.2778075632517951</v>
       </c>
       <c r="G90">
-        <v>1.333772243768696</v>
+        <v>1.715065986463794</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_sp + iqr_t1_Levo_sp + iqr_t2_Levo_sp + iqr_t3_Levo_sp</t>
+          <t>pct1_Levo_sp + t1_Levo_sp + t2_Levo_sp + t3_Levo_sp</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -6035,32 +6035,32 @@
         </is>
       </c>
       <c r="O90">
-        <v>15307</v>
+        <v>15241</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_sp + iqr_t1_Levo_sp + iqr_t2_Levo_sp + iqr_t3_Levo_sp</t>
+          <t>t1_Levo_sp</t>
         </is>
       </c>
       <c r="B91">
-        <v>1.444060473786928</v>
+        <v>1.221772734126106</v>
       </c>
       <c r="C91">
-        <v>0.3088405435581874</v>
+        <v>0.4458415140723057</v>
       </c>
       <c r="D91">
-        <v>1.189801425402284</v>
+        <v>0.449269210046113</v>
       </c>
       <c r="E91">
-        <v>0.2341244492259534</v>
+        <v>0.6532374661463523</v>
       </c>
       <c r="F91">
-        <v>0.7883150783713755</v>
+        <v>0.5099052037393764</v>
       </c>
       <c r="G91">
-        <v>2.645275612718063</v>
+        <v>2.927462992938873</v>
       </c>
       <c r="H91" t="inlineStr">
         <is>
@@ -6069,7 +6069,7 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_sp + iqr_t1_Levo_sp + iqr_t2_Levo_sp + iqr_t3_Levo_sp</t>
+          <t>pct1_Levo_sp + t1_Levo_sp + t2_Levo_sp + t3_Levo_sp</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -6098,32 +6098,32 @@
         </is>
       </c>
       <c r="O91">
-        <v>15307</v>
+        <v>15241</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_sp + iqr_t1_Levo_sp + iqr_t2_Levo_sp + iqr_t3_Levo_sp</t>
+          <t>t2_Levo_sp</t>
         </is>
       </c>
       <c r="B92">
-        <v>0.5743456129061534</v>
+        <v>0.6151256128551696</v>
       </c>
       <c r="C92">
-        <v>0.3301547711512277</v>
+        <v>0.466306954611472</v>
       </c>
       <c r="D92">
-        <v>-1.679587875860187</v>
+        <v>-1.042079211302776</v>
       </c>
       <c r="E92">
-        <v>0.09303752823340861</v>
+        <v>0.2973749559063733</v>
       </c>
       <c r="F92">
-        <v>0.3007080520792597</v>
+        <v>0.2466281307698092</v>
       </c>
       <c r="G92">
-        <v>1.096987196663421</v>
+        <v>1.534210709903199</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
@@ -6132,7 +6132,7 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_sp + iqr_t1_Levo_sp + iqr_t2_Levo_sp + iqr_t3_Levo_sp</t>
+          <t>pct1_Levo_sp + t1_Levo_sp + t2_Levo_sp + t3_Levo_sp</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -6161,32 +6161,32 @@
         </is>
       </c>
       <c r="O92">
-        <v>15307</v>
+        <v>15241</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_sp + iqr_t1_Levo_sp + iqr_t2_Levo_sp + iqr_t3_Levo_sp</t>
+          <t>t3_Levo_sp</t>
         </is>
       </c>
       <c r="B93">
-        <v>1.552700140258968</v>
+        <v>1.475735236994688</v>
       </c>
       <c r="C93">
-        <v>0.2867518246278473</v>
+        <v>0.4401491647206917</v>
       </c>
       <c r="D93">
-        <v>1.534412002114798</v>
+        <v>0.8841464724920141</v>
       </c>
       <c r="E93">
-        <v>0.1249283267747124</v>
+        <v>0.3766171491605744</v>
       </c>
       <c r="F93">
-        <v>0.8851237551396194</v>
+        <v>0.6228060160917467</v>
       </c>
       <c r="G93">
-        <v>2.723774739476885</v>
+        <v>3.496746070909746</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
@@ -6195,7 +6195,7 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_sp + iqr_t1_Levo_sp + iqr_t2_Levo_sp + iqr_t3_Levo_sp</t>
+          <t>pct1_Levo_sp + t1_Levo_sp + t2_Levo_sp + t3_Levo_sp</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -6224,32 +6224,32 @@
         </is>
       </c>
       <c r="O93">
-        <v>15307</v>
+        <v>15241</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_sp + iqr_t1_K_sp + iqr_t2_K_sp + iqr_t3_K_sp</t>
+          <t>pct1_K_sp</t>
         </is>
       </c>
       <c r="B94">
-        <v>0.6250007582769395</v>
+        <v>0.6674714410828895</v>
       </c>
       <c r="C94">
-        <v>0.248743985149407</v>
+        <v>0.2830204123215</v>
       </c>
       <c r="D94">
-        <v>-1.889502637505239</v>
+        <v>-1.428372855518131</v>
       </c>
       <c r="E94">
-        <v>0.05882450969693344</v>
+        <v>0.1531845678815741</v>
       </c>
       <c r="F94">
-        <v>0.3838391600145142</v>
+        <v>0.3832880477571084</v>
       </c>
       <c r="G94">
-        <v>1.017681332545586</v>
+        <v>1.162358511485848</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
@@ -6258,7 +6258,7 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_sp + iqr_t1_K_sp + iqr_t2_K_sp + iqr_t3_K_sp</t>
+          <t>pct1_K_sp + t1_K_sp + t2_K_sp + t3_K_sp</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -6287,32 +6287,32 @@
         </is>
       </c>
       <c r="O94">
-        <v>15307</v>
+        <v>15241</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_sp + iqr_t1_K_sp + iqr_t2_K_sp + iqr_t3_K_sp</t>
+          <t>t1_K_sp</t>
         </is>
       </c>
       <c r="B95">
-        <v>1.390957843593314</v>
+        <v>1.129879089873946</v>
       </c>
       <c r="C95">
-        <v>0.2567487298397837</v>
+        <v>0.2690744108153745</v>
       </c>
       <c r="D95">
-        <v>1.285274541148119</v>
+        <v>0.4538173158783318</v>
       </c>
       <c r="E95">
-        <v>0.1986963634174375</v>
+        <v>0.6499603194055776</v>
       </c>
       <c r="F95">
-        <v>0.8409478271406442</v>
+        <v>0.6667997337026752</v>
       </c>
       <c r="G95">
-        <v>2.300694121812842</v>
+        <v>1.914557989766118</v>
       </c>
       <c r="H95" t="inlineStr">
         <is>
@@ -6321,7 +6321,7 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_sp + iqr_t1_K_sp + iqr_t2_K_sp + iqr_t3_K_sp</t>
+          <t>pct1_K_sp + t1_K_sp + t2_K_sp + t3_K_sp</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -6350,32 +6350,32 @@
         </is>
       </c>
       <c r="O95">
-        <v>15307</v>
+        <v>15241</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_sp + iqr_t1_K_sp + iqr_t2_K_sp + iqr_t3_K_sp</t>
+          <t>t2_K_sp</t>
         </is>
       </c>
       <c r="B96">
-        <v>0.5079280879100945</v>
+        <v>0.6246763633123051</v>
       </c>
       <c r="C96">
-        <v>0.2788630915530074</v>
+        <v>0.2789002962209596</v>
       </c>
       <c r="D96">
-        <v>-2.429204226646252</v>
+        <v>-1.687060173244414</v>
       </c>
       <c r="E96">
-        <v>0.01513200590825685</v>
+        <v>0.09159178212365927</v>
       </c>
       <c r="F96">
-        <v>0.2940583633004204</v>
+        <v>0.3616218892264428</v>
       </c>
       <c r="G96">
-        <v>0.8773460465208126</v>
+        <v>1.079084453974345</v>
       </c>
       <c r="H96" t="inlineStr">
         <is>
@@ -6384,7 +6384,7 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_sp + iqr_t1_K_sp + iqr_t2_K_sp + iqr_t3_K_sp</t>
+          <t>pct1_K_sp + t1_K_sp + t2_K_sp + t3_K_sp</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -6413,32 +6413,32 @@
         </is>
       </c>
       <c r="O96">
-        <v>15307</v>
+        <v>15241</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_sp + iqr_t1_K_sp + iqr_t2_K_sp + iqr_t3_K_sp</t>
+          <t>t3_K_sp</t>
         </is>
       </c>
       <c r="B97">
-        <v>1.457504910878655</v>
+        <v>1.318409800017897</v>
       </c>
       <c r="C97">
-        <v>0.2210851825263589</v>
+        <v>0.2645657872720994</v>
       </c>
       <c r="D97">
-        <v>1.70398578646007</v>
+        <v>1.044830158357355</v>
       </c>
       <c r="E97">
-        <v>0.08838374267369423</v>
+        <v>0.2961014736637475</v>
       </c>
       <c r="F97">
-        <v>0.9449786100188253</v>
+        <v>0.784967391790131</v>
       </c>
       <c r="G97">
-        <v>2.24800915355436</v>
+        <v>2.214365104796556</v>
       </c>
       <c r="H97" t="inlineStr">
         <is>
@@ -6447,7 +6447,7 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_sp + iqr_t1_K_sp + iqr_t2_K_sp + iqr_t3_K_sp</t>
+          <t>pct1_K_sp + t1_K_sp + t2_K_sp + t3_K_sp</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -6476,43 +6476,43 @@
         </is>
       </c>
       <c r="O97">
-        <v>15307</v>
+        <v>15241</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
+          <t>iqr_pct1_PM25_cs</t>
+        </is>
+      </c>
+      <c r="B98">
+        <v>0.5611963433945723</v>
+      </c>
+      <c r="C98">
+        <v>0.6587984375907654</v>
+      </c>
+      <c r="D98">
+        <v>-0.8768758599033931</v>
+      </c>
+      <c r="E98">
+        <v>0.3805540693745468</v>
+      </c>
+      <c r="F98">
+        <v>0.1542924182543567</v>
+      </c>
+      <c r="G98">
+        <v>2.041197742589311</v>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>malf_card_bin</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
           <t>iqr_pct1_PM25_cs + iqr_t1_PM25_cs + iqr_t2_PM25_cs + iqr_t3_PM25_cs</t>
         </is>
       </c>
-      <c r="B98">
-        <v>0.7443285454002992</v>
-      </c>
-      <c r="C98">
-        <v>0.653282028263939</v>
-      </c>
-      <c r="D98">
-        <v>-0.4519835776400614</v>
-      </c>
-      <c r="E98">
-        <v>0.6512808132155066</v>
-      </c>
-      <c r="F98">
-        <v>0.2068664225949006</v>
-      </c>
-      <c r="G98">
-        <v>2.678177427482532</v>
-      </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>malf_card_bin</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>iqr_pct1_PM25_cs + iqr_t1_PM25_cs + iqr_t2_PM25_cs + iqr_t3_PM25_cs</t>
-        </is>
-      </c>
       <c r="J98" t="inlineStr">
         <is>
           <t>pct1_t1_t2_t3</t>
@@ -6539,43 +6539,43 @@
         </is>
       </c>
       <c r="O98">
-        <v>15307</v>
+        <v>15241</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
+          <t>iqr_t1_PM25_cs</t>
+        </is>
+      </c>
+      <c r="B99">
+        <v>1.507791769641759</v>
+      </c>
+      <c r="C99">
+        <v>0.565408926737085</v>
+      </c>
+      <c r="D99">
+        <v>0.7262817349368335</v>
+      </c>
+      <c r="E99">
+        <v>0.4676660741675793</v>
+      </c>
+      <c r="F99">
+        <v>0.497810918051472</v>
+      </c>
+      <c r="G99">
+        <v>4.566866531369171</v>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>malf_card_bin</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
           <t>iqr_pct1_PM25_cs + iqr_t1_PM25_cs + iqr_t2_PM25_cs + iqr_t3_PM25_cs</t>
         </is>
       </c>
-      <c r="B99">
-        <v>1.885954907154599</v>
-      </c>
-      <c r="C99">
-        <v>0.5042084762128685</v>
-      </c>
-      <c r="D99">
-        <v>1.258277685930135</v>
-      </c>
-      <c r="E99">
-        <v>0.2082913481663285</v>
-      </c>
-      <c r="F99">
-        <v>0.7020180385112033</v>
-      </c>
-      <c r="G99">
-        <v>5.066573388005259</v>
-      </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>malf_card_bin</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>iqr_pct1_PM25_cs + iqr_t1_PM25_cs + iqr_t2_PM25_cs + iqr_t3_PM25_cs</t>
-        </is>
-      </c>
       <c r="J99" t="inlineStr">
         <is>
           <t>pct1_t1_t2_t3</t>
@@ -6602,43 +6602,43 @@
         </is>
       </c>
       <c r="O99">
-        <v>15307</v>
+        <v>15241</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
+          <t>iqr_t2_PM25_cs</t>
+        </is>
+      </c>
+      <c r="B100">
+        <v>0.9754168913042175</v>
+      </c>
+      <c r="C100">
+        <v>0.6686245268275169</v>
+      </c>
+      <c r="D100">
+        <v>-0.03722615241798326</v>
+      </c>
+      <c r="E100">
+        <v>0.9703046864463435</v>
+      </c>
+      <c r="F100">
+        <v>0.2630607433121601</v>
+      </c>
+      <c r="G100">
+        <v>3.616800058656274</v>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>malf_card_bin</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
           <t>iqr_pct1_PM25_cs + iqr_t1_PM25_cs + iqr_t2_PM25_cs + iqr_t3_PM25_cs</t>
         </is>
       </c>
-      <c r="B100">
-        <v>0.8066015888502903</v>
-      </c>
-      <c r="C100">
-        <v>0.5860413045395454</v>
-      </c>
-      <c r="D100">
-        <v>-0.3667410898652654</v>
-      </c>
-      <c r="E100">
-        <v>0.7138121536323323</v>
-      </c>
-      <c r="F100">
-        <v>0.2557524544616958</v>
-      </c>
-      <c r="G100">
-        <v>2.543890045963388</v>
-      </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>malf_card_bin</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>iqr_pct1_PM25_cs + iqr_t1_PM25_cs + iqr_t2_PM25_cs + iqr_t3_PM25_cs</t>
-        </is>
-      </c>
       <c r="J100" t="inlineStr">
         <is>
           <t>pct1_t1_t2_t3</t>
@@ -6665,43 +6665,43 @@
         </is>
       </c>
       <c r="O100">
-        <v>15307</v>
+        <v>15241</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
+          <t>iqr_t3_PM25_cs</t>
+        </is>
+      </c>
+      <c r="B101">
+        <v>2.02307466556454</v>
+      </c>
+      <c r="C101">
+        <v>0.5633779389825878</v>
+      </c>
+      <c r="D101">
+        <v>1.250702977673201</v>
+      </c>
+      <c r="E101">
+        <v>0.2110428636900488</v>
+      </c>
+      <c r="F101">
+        <v>0.6706002955339189</v>
+      </c>
+      <c r="G101">
+        <v>6.103234862415983</v>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>malf_card_bin</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
           <t>iqr_pct1_PM25_cs + iqr_t1_PM25_cs + iqr_t2_PM25_cs + iqr_t3_PM25_cs</t>
         </is>
       </c>
-      <c r="B101">
-        <v>2.846599554418186</v>
-      </c>
-      <c r="C101">
-        <v>0.5710448653439697</v>
-      </c>
-      <c r="D101">
-        <v>1.83194912801292</v>
-      </c>
-      <c r="E101">
-        <v>0.0669590001743595</v>
-      </c>
-      <c r="F101">
-        <v>0.9295058050366293</v>
-      </c>
-      <c r="G101">
-        <v>8.717674466696307</v>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>malf_card_bin</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>iqr_pct1_PM25_cs + iqr_t1_PM25_cs + iqr_t2_PM25_cs + iqr_t3_PM25_cs</t>
-        </is>
-      </c>
       <c r="J101" t="inlineStr">
         <is>
           <t>pct1_t1_t2_t3</t>
@@ -6728,32 +6728,32 @@
         </is>
       </c>
       <c r="O101">
-        <v>15307</v>
+        <v>15241</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_cs + iqr_t1_Levo_cs + iqr_t2_Levo_cs + iqr_t3_Levo_cs</t>
+          <t>pct1_Levo_cs</t>
         </is>
       </c>
       <c r="B102">
-        <v>0.4700212094717467</v>
+        <v>0.2413025008900541</v>
       </c>
       <c r="C102">
-        <v>0.7193808639896363</v>
+        <v>1.053375499506703</v>
       </c>
       <c r="D102">
-        <v>-1.04948226531009</v>
+        <v>-1.349664903764165</v>
       </c>
       <c r="E102">
-        <v>0.2939562133712376</v>
+        <v>0.1771234948876623</v>
       </c>
       <c r="F102">
-        <v>0.114757044339339</v>
+        <v>0.03061448599845494</v>
       </c>
       <c r="G102">
-        <v>1.925110032461439</v>
+        <v>1.901939393616903</v>
       </c>
       <c r="H102" t="inlineStr">
         <is>
@@ -6762,7 +6762,7 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_cs + iqr_t1_Levo_cs + iqr_t2_Levo_cs + iqr_t3_Levo_cs</t>
+          <t>pct1_Levo_cs + t1_Levo_cs + t2_Levo_cs + t3_Levo_cs</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -6791,32 +6791,32 @@
         </is>
       </c>
       <c r="O102">
-        <v>15307</v>
+        <v>15241</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_cs + iqr_t1_Levo_cs + iqr_t2_Levo_cs + iqr_t3_Levo_cs</t>
+          <t>t1_Levo_cs</t>
         </is>
       </c>
       <c r="B103">
-        <v>1.606195786328333</v>
+        <v>1.439627466651508</v>
       </c>
       <c r="C103">
-        <v>0.5683807727071319</v>
+        <v>0.9447958349512449</v>
       </c>
       <c r="D103">
-        <v>0.8337166564108167</v>
+        <v>0.3856752569436377</v>
       </c>
       <c r="E103">
-        <v>0.4044406697928857</v>
+        <v>0.6997371898473943</v>
       </c>
       <c r="F103">
-        <v>0.5272200177277159</v>
+        <v>0.2259635823262201</v>
       </c>
       <c r="G103">
-        <v>4.893336400878601</v>
+        <v>9.171952495182888</v>
       </c>
       <c r="H103" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_cs + iqr_t1_Levo_cs + iqr_t2_Levo_cs + iqr_t3_Levo_cs</t>
+          <t>pct1_Levo_cs + t1_Levo_cs + t2_Levo_cs + t3_Levo_cs</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -6854,32 +6854,32 @@
         </is>
       </c>
       <c r="O103">
-        <v>15307</v>
+        <v>15241</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_cs + iqr_t1_Levo_cs + iqr_t2_Levo_cs + iqr_t3_Levo_cs</t>
+          <t>t2_Levo_cs</t>
         </is>
       </c>
       <c r="B104">
-        <v>0.5430513645056489</v>
+        <v>0.5487395652028071</v>
       </c>
       <c r="C104">
-        <v>0.6423656729896238</v>
+        <v>1.097878129404911</v>
       </c>
       <c r="D104">
-        <v>-0.950473219945445</v>
+        <v>-0.5466283681911008</v>
       </c>
       <c r="E104">
-        <v>0.3418718550407422</v>
+        <v>0.5846340755391206</v>
       </c>
       <c r="F104">
-        <v>0.1541907273538006</v>
+        <v>0.06380441289455344</v>
       </c>
       <c r="G104">
-        <v>1.912597401624347</v>
+        <v>4.719346151129148</v>
       </c>
       <c r="H104" t="inlineStr">
         <is>
@@ -6888,7 +6888,7 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_cs + iqr_t1_Levo_cs + iqr_t2_Levo_cs + iqr_t3_Levo_cs</t>
+          <t>pct1_Levo_cs + t1_Levo_cs + t2_Levo_cs + t3_Levo_cs</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -6917,32 +6917,32 @@
         </is>
       </c>
       <c r="O104">
-        <v>15307</v>
+        <v>15241</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_cs + iqr_t1_Levo_cs + iqr_t2_Levo_cs + iqr_t3_Levo_cs</t>
+          <t>t3_Levo_cs</t>
         </is>
       </c>
       <c r="B105">
-        <v>2.138326931407289</v>
+        <v>2.178660564114182</v>
       </c>
       <c r="C105">
-        <v>0.6422779419835366</v>
+        <v>0.9487045026200098</v>
       </c>
       <c r="D105">
-        <v>1.183325264389318</v>
+        <v>0.8208143480777687</v>
       </c>
       <c r="E105">
-        <v>0.236680263760424</v>
+        <v>0.4117520245680722</v>
       </c>
       <c r="F105">
-        <v>0.607248052101013</v>
+        <v>0.3393523301760364</v>
       </c>
       <c r="G105">
-        <v>7.5297764229322</v>
+        <v>13.98712026277846</v>
       </c>
       <c r="H105" t="inlineStr">
         <is>
@@ -6951,7 +6951,7 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_cs + iqr_t1_Levo_cs + iqr_t2_Levo_cs + iqr_t3_Levo_cs</t>
+          <t>pct1_Levo_cs + t1_Levo_cs + t2_Levo_cs + t3_Levo_cs</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -6980,32 +6980,32 @@
         </is>
       </c>
       <c r="O105">
-        <v>15307</v>
+        <v>15241</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_cs + iqr_t1_K_cs + iqr_t2_K_cs + iqr_t3_K_cs</t>
+          <t>pct1_K_cs</t>
         </is>
       </c>
       <c r="B106">
-        <v>0.5229570604874539</v>
+        <v>0.2736008351306278</v>
       </c>
       <c r="C106">
-        <v>0.6425600408239934</v>
+        <v>0.9204218481430264</v>
       </c>
       <c r="D106">
-        <v>-1.008864354177611</v>
+        <v>-1.408142411520606</v>
       </c>
       <c r="E106">
-        <v>0.3130396924880292</v>
+        <v>0.1590889047064739</v>
       </c>
       <c r="F106">
-        <v>0.1484287166529931</v>
+        <v>0.04504565653900337</v>
       </c>
       <c r="G106">
-        <v>1.842528139302374</v>
+        <v>1.66181209767385</v>
       </c>
       <c r="H106" t="inlineStr">
         <is>
@@ -7014,7 +7014,7 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_cs + iqr_t1_K_cs + iqr_t2_K_cs + iqr_t3_K_cs</t>
+          <t>pct1_K_cs + t1_K_cs + t2_K_cs + t3_K_cs</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
@@ -7043,32 +7043,32 @@
         </is>
       </c>
       <c r="O106">
-        <v>15307</v>
+        <v>15241</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_cs + iqr_t1_K_cs + iqr_t2_K_cs + iqr_t3_K_cs</t>
+          <t>t1_K_cs</t>
         </is>
       </c>
       <c r="B107">
-        <v>1.669955979266788</v>
+        <v>1.482704540856866</v>
       </c>
       <c r="C107">
-        <v>0.4944084196553611</v>
+        <v>0.8165861332756814</v>
       </c>
       <c r="D107">
-        <v>1.037193635816743</v>
+        <v>0.4823346816049991</v>
       </c>
       <c r="E107">
-        <v>0.2996456234639284</v>
+        <v>0.6295682138824457</v>
       </c>
       <c r="F107">
-        <v>0.6336709726647215</v>
+        <v>0.2992094051956055</v>
       </c>
       <c r="G107">
-        <v>4.400947957204978</v>
+        <v>7.347405252987876</v>
       </c>
       <c r="H107" t="inlineStr">
         <is>
@@ -7077,7 +7077,7 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_cs + iqr_t1_K_cs + iqr_t2_K_cs + iqr_t3_K_cs</t>
+          <t>pct1_K_cs + t1_K_cs + t2_K_cs + t3_K_cs</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -7106,32 +7106,32 @@
         </is>
       </c>
       <c r="O107">
-        <v>15307</v>
+        <v>15241</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_cs + iqr_t1_K_cs + iqr_t2_K_cs + iqr_t3_K_cs</t>
+          <t>t2_K_cs</t>
         </is>
       </c>
       <c r="B108">
-        <v>0.5888450492162223</v>
+        <v>0.5961436690131283</v>
       </c>
       <c r="C108">
-        <v>0.5741503707231005</v>
+        <v>0.9637973815215831</v>
       </c>
       <c r="D108">
-        <v>-0.9223928630568966</v>
+        <v>-0.5367036635419945</v>
       </c>
       <c r="E108">
-        <v>0.3563236911212728</v>
+        <v>0.5914723250461114</v>
       </c>
       <c r="F108">
-        <v>0.1911099709278122</v>
+        <v>0.09014987267057871</v>
       </c>
       <c r="G108">
-        <v>1.814340143023874</v>
+        <v>3.942182762731937</v>
       </c>
       <c r="H108" t="inlineStr">
         <is>
@@ -7140,7 +7140,7 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_cs + iqr_t1_K_cs + iqr_t2_K_cs + iqr_t3_K_cs</t>
+          <t>pct1_K_cs + t1_K_cs + t2_K_cs + t3_K_cs</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -7169,32 +7169,32 @@
         </is>
       </c>
       <c r="O108">
-        <v>15307</v>
+        <v>15241</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_cs + iqr_t1_K_cs + iqr_t2_K_cs + iqr_t3_K_cs</t>
+          <t>t3_K_cs</t>
         </is>
       </c>
       <c r="B109">
-        <v>2.308328054253949</v>
+        <v>2.255067099882446</v>
       </c>
       <c r="C109">
-        <v>0.5540017900731129</v>
+        <v>0.8206405340108425</v>
       </c>
       <c r="D109">
-        <v>1.509965295105782</v>
+        <v>0.9909085584439653</v>
       </c>
       <c r="E109">
-        <v>0.1310522799154763</v>
+        <v>0.321730232910547</v>
       </c>
       <c r="F109">
-        <v>0.7793460725300756</v>
+        <v>0.4514700863020211</v>
       </c>
       <c r="G109">
-        <v>6.836986281021129</v>
+        <v>11.26393038933321</v>
       </c>
       <c r="H109" t="inlineStr">
         <is>
@@ -7203,7 +7203,7 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_cs + iqr_t1_K_cs + iqr_t2_K_cs + iqr_t3_K_cs</t>
+          <t>pct1_K_cs + t1_K_cs + t2_K_cs + t3_K_cs</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -7232,43 +7232,43 @@
         </is>
       </c>
       <c r="O109">
-        <v>15307</v>
+        <v>15241</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
+          <t>iqr_pct1_PM25_sp</t>
+        </is>
+      </c>
+      <c r="B110">
+        <v>0.5296154845186619</v>
+      </c>
+      <c r="C110">
+        <v>0.3744489570066666</v>
+      </c>
+      <c r="D110">
+        <v>-1.697438395150827</v>
+      </c>
+      <c r="E110">
+        <v>0.08961380878449922</v>
+      </c>
+      <c r="F110">
+        <v>0.2542313737233444</v>
+      </c>
+      <c r="G110">
+        <v>1.103296408047459</v>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>malf_card_bin</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
           <t>iqr_pct1_PM25_sp + iqr_t1_PM25_sp + iqr_t2_PM25_sp + iqr_t3_PM25_sp</t>
         </is>
       </c>
-      <c r="B110">
-        <v>0.4977575404011669</v>
-      </c>
-      <c r="C110">
-        <v>0.3292388225496248</v>
-      </c>
-      <c r="D110">
-        <v>-2.118954811517443</v>
-      </c>
-      <c r="E110">
-        <v>0.0340942860637355</v>
-      </c>
-      <c r="F110">
-        <v>0.2610773849119652</v>
-      </c>
-      <c r="G110">
-        <v>0.9490005007893134</v>
-      </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>malf_card_bin</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>iqr_pct1_PM25_sp + iqr_t1_PM25_sp + iqr_t2_PM25_sp + iqr_t3_PM25_sp</t>
-        </is>
-      </c>
       <c r="J110" t="inlineStr">
         <is>
           <t>pct1_t1_t2_t3</t>
@@ -7295,43 +7295,43 @@
         </is>
       </c>
       <c r="O110">
-        <v>15307</v>
+        <v>15241</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
+          <t>iqr_t1_PM25_sp</t>
+        </is>
+      </c>
+      <c r="B111">
+        <v>1.251221152954467</v>
+      </c>
+      <c r="C111">
+        <v>0.3660004097222353</v>
+      </c>
+      <c r="D111">
+        <v>0.6123490325318951</v>
+      </c>
+      <c r="E111">
+        <v>0.5403068551982633</v>
+      </c>
+      <c r="F111">
+        <v>0.6106522537803358</v>
+      </c>
+      <c r="G111">
+        <v>2.563741251930053</v>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>malf_card_bin</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
           <t>iqr_pct1_PM25_sp + iqr_t1_PM25_sp + iqr_t2_PM25_sp + iqr_t3_PM25_sp</t>
         </is>
       </c>
-      <c r="B111">
-        <v>1.553099410001191</v>
-      </c>
-      <c r="C111">
-        <v>0.3669903616282901</v>
-      </c>
-      <c r="D111">
-        <v>1.199629744377448</v>
-      </c>
-      <c r="E111">
-        <v>0.2302831693471984</v>
-      </c>
-      <c r="F111">
-        <v>0.7565131692651728</v>
-      </c>
-      <c r="G111">
-        <v>3.188467663674674</v>
-      </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>malf_card_bin</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>iqr_pct1_PM25_sp + iqr_t1_PM25_sp + iqr_t2_PM25_sp + iqr_t3_PM25_sp</t>
-        </is>
-      </c>
       <c r="J111" t="inlineStr">
         <is>
           <t>pct1_t1_t2_t3</t>
@@ -7358,43 +7358,43 @@
         </is>
       </c>
       <c r="O111">
-        <v>15307</v>
+        <v>15241</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
+          <t>iqr_t2_PM25_sp</t>
+        </is>
+      </c>
+      <c r="B112">
+        <v>0.7396844931401748</v>
+      </c>
+      <c r="C112">
+        <v>0.3588176222875661</v>
+      </c>
+      <c r="D112">
+        <v>-0.8403476462512884</v>
+      </c>
+      <c r="E112">
+        <v>0.4007134940329197</v>
+      </c>
+      <c r="F112">
+        <v>0.3661174259807113</v>
+      </c>
+      <c r="G112">
+        <v>1.494419851572055</v>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>malf_card_bin</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
           <t>iqr_pct1_PM25_sp + iqr_t1_PM25_sp + iqr_t2_PM25_sp + iqr_t3_PM25_sp</t>
         </is>
       </c>
-      <c r="B112">
-        <v>0.5284044528266615</v>
-      </c>
-      <c r="C112">
-        <v>0.3750452353357624</v>
-      </c>
-      <c r="D112">
-        <v>-1.700843576371945</v>
-      </c>
-      <c r="E112">
-        <v>0.08897236409898256</v>
-      </c>
-      <c r="F112">
-        <v>0.2533537784543633</v>
-      </c>
-      <c r="G112">
-        <v>1.102060792108289</v>
-      </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>malf_card_bin</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>iqr_pct1_PM25_sp + iqr_t1_PM25_sp + iqr_t2_PM25_sp + iqr_t3_PM25_sp</t>
-        </is>
-      </c>
       <c r="J112" t="inlineStr">
         <is>
           <t>pct1_t1_t2_t3</t>
@@ -7421,43 +7421,43 @@
         </is>
       </c>
       <c r="O112">
-        <v>15307</v>
+        <v>15241</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
+          <t>iqr_t3_PM25_sp</t>
+        </is>
+      </c>
+      <c r="B113">
+        <v>1.405619077074693</v>
+      </c>
+      <c r="C113">
+        <v>0.3257211485572266</v>
+      </c>
+      <c r="D113">
+        <v>1.045304646320749</v>
+      </c>
+      <c r="E113">
+        <v>0.2958821909206885</v>
+      </c>
+      <c r="F113">
+        <v>0.7423578383166365</v>
+      </c>
+      <c r="G113">
+        <v>2.66147252424321</v>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>malf_card_bin</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
           <t>iqr_pct1_PM25_sp + iqr_t1_PM25_sp + iqr_t2_PM25_sp + iqr_t3_PM25_sp</t>
         </is>
       </c>
-      <c r="B113">
-        <v>1.640841035396948</v>
-      </c>
-      <c r="C113">
-        <v>0.2833032210886009</v>
-      </c>
-      <c r="D113">
-        <v>1.747982020621774</v>
-      </c>
-      <c r="E113">
-        <v>0.08046714076401304</v>
-      </c>
-      <c r="F113">
-        <v>0.941712574863386</v>
-      </c>
-      <c r="G113">
-        <v>2.859003240806365</v>
-      </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>malf_card_bin</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>iqr_pct1_PM25_sp + iqr_t1_PM25_sp + iqr_t2_PM25_sp + iqr_t3_PM25_sp</t>
-        </is>
-      </c>
       <c r="J113" t="inlineStr">
         <is>
           <t>pct1_t1_t2_t3</t>
@@ -7484,32 +7484,32 @@
         </is>
       </c>
       <c r="O113">
-        <v>15307</v>
+        <v>15241</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_sp + iqr_t1_Levo_sp + iqr_t2_Levo_sp + iqr_t3_Levo_sp</t>
+          <t>pct1_Levo_sp</t>
         </is>
       </c>
       <c r="B114">
-        <v>0.5288617256242186</v>
+        <v>0.3941859083125845</v>
       </c>
       <c r="C114">
-        <v>0.4299906999450674</v>
+        <v>0.6601931199037497</v>
       </c>
       <c r="D114">
-        <v>-1.481493133705147</v>
+        <v>-1.410091387496328</v>
       </c>
       <c r="E114">
-        <v>0.1384752132716894</v>
+        <v>0.1585127000188225</v>
       </c>
       <c r="F114">
-        <v>0.2276844601891077</v>
+        <v>0.1080795909198227</v>
       </c>
       <c r="G114">
-        <v>1.228431332546457</v>
+        <v>1.437667639096503</v>
       </c>
       <c r="H114" t="inlineStr">
         <is>
@@ -7518,7 +7518,7 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_sp + iqr_t1_Levo_sp + iqr_t2_Levo_sp + iqr_t3_Levo_sp</t>
+          <t>pct1_Levo_sp + t1_Levo_sp + t2_Levo_sp + t3_Levo_sp</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
@@ -7547,32 +7547,32 @@
         </is>
       </c>
       <c r="O114">
-        <v>15307</v>
+        <v>15241</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_sp + iqr_t1_Levo_sp + iqr_t2_Levo_sp + iqr_t3_Levo_sp</t>
+          <t>t1_Levo_sp</t>
         </is>
       </c>
       <c r="B115">
-        <v>1.738130738843581</v>
+        <v>1.706139599675051</v>
       </c>
       <c r="C115">
-        <v>0.4368612272749875</v>
+        <v>0.629565518999464</v>
       </c>
       <c r="D115">
-        <v>1.265413850509897</v>
+        <v>0.8485745458544992</v>
       </c>
       <c r="E115">
-        <v>0.2057230127504262</v>
+        <v>0.3961180757038457</v>
       </c>
       <c r="F115">
-        <v>0.7382874556221795</v>
+        <v>0.4967380427622075</v>
       </c>
       <c r="G115">
-        <v>4.092035483342937</v>
+        <v>5.860055165883119</v>
       </c>
       <c r="H115" t="inlineStr">
         <is>
@@ -7581,7 +7581,7 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_sp + iqr_t1_Levo_sp + iqr_t2_Levo_sp + iqr_t3_Levo_sp</t>
+          <t>pct1_Levo_sp + t1_Levo_sp + t2_Levo_sp + t3_Levo_sp</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -7610,32 +7610,32 @@
         </is>
       </c>
       <c r="O115">
-        <v>15307</v>
+        <v>15241</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_sp + iqr_t1_Levo_sp + iqr_t2_Levo_sp + iqr_t3_Levo_sp</t>
+          <t>t2_Levo_sp</t>
         </is>
       </c>
       <c r="B116">
-        <v>0.5270575760339146</v>
+        <v>0.6842824254539481</v>
       </c>
       <c r="C116">
-        <v>0.4648342830295127</v>
+        <v>0.6455249775263305</v>
       </c>
       <c r="D116">
-        <v>-1.377793134787897</v>
+        <v>-0.5877147392867964</v>
       </c>
       <c r="E116">
-        <v>0.1682671662442555</v>
+        <v>0.5567237806146139</v>
       </c>
       <c r="F116">
-        <v>0.2119290060557584</v>
+        <v>0.1930916657144924</v>
       </c>
       <c r="G116">
-        <v>1.310767665194728</v>
+        <v>2.424974874252143</v>
       </c>
       <c r="H116" t="inlineStr">
         <is>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_sp + iqr_t1_Levo_sp + iqr_t2_Levo_sp + iqr_t3_Levo_sp</t>
+          <t>pct1_Levo_sp + t1_Levo_sp + t2_Levo_sp + t3_Levo_sp</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -7673,32 +7673,32 @@
         </is>
       </c>
       <c r="O116">
-        <v>15307</v>
+        <v>15241</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_sp + iqr_t1_Levo_sp + iqr_t2_Levo_sp + iqr_t3_Levo_sp</t>
+          <t>t3_Levo_sp</t>
         </is>
       </c>
       <c r="B117">
-        <v>1.975372651160216</v>
+        <v>2.153193064360158</v>
       </c>
       <c r="C117">
-        <v>0.3865600276573943</v>
+        <v>0.5975978679669381</v>
       </c>
       <c r="D117">
-        <v>1.761064300444377</v>
+        <v>1.283391269824753</v>
       </c>
       <c r="E117">
-        <v>0.07822752047685226</v>
+        <v>0.1993550309120002</v>
       </c>
       <c r="F117">
-        <v>0.9259947930711597</v>
+        <v>0.6674315693181584</v>
       </c>
       <c r="G117">
-        <v>4.213951460796038</v>
+        <v>6.946390589742441</v>
       </c>
       <c r="H117" t="inlineStr">
         <is>
@@ -7707,7 +7707,7 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_sp + iqr_t1_Levo_sp + iqr_t2_Levo_sp + iqr_t3_Levo_sp</t>
+          <t>pct1_Levo_sp + t1_Levo_sp + t2_Levo_sp + t3_Levo_sp</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
@@ -7736,32 +7736,32 @@
         </is>
       </c>
       <c r="O117">
-        <v>15307</v>
+        <v>15241</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_sp + iqr_t1_K_sp + iqr_t2_K_sp + iqr_t3_K_sp</t>
+          <t>pct1_K_sp</t>
         </is>
       </c>
       <c r="B118">
-        <v>0.4418769566583282</v>
+        <v>0.422001595777874</v>
       </c>
       <c r="C118">
-        <v>0.3444798922163252</v>
+        <v>0.4063910340792304</v>
       </c>
       <c r="D118">
-        <v>-2.370889659205822</v>
+        <v>-2.12294590958155</v>
       </c>
       <c r="E118">
-        <v>0.01774532783290857</v>
+        <v>0.03375838474272114</v>
       </c>
       <c r="F118">
-        <v>0.2249466544093713</v>
+        <v>0.1902801205412112</v>
       </c>
       <c r="G118">
-        <v>0.868006885180381</v>
+        <v>0.9359114674331003</v>
       </c>
       <c r="H118" t="inlineStr">
         <is>
@@ -7770,7 +7770,7 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_sp + iqr_t1_K_sp + iqr_t2_K_sp + iqr_t3_K_sp</t>
+          <t>pct1_K_sp + t1_K_sp + t2_K_sp + t3_K_sp</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -7799,32 +7799,32 @@
         </is>
       </c>
       <c r="O118">
-        <v>15307</v>
+        <v>15241</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_sp + iqr_t1_K_sp + iqr_t2_K_sp + iqr_t3_K_sp</t>
+          <t>t1_K_sp</t>
         </is>
       </c>
       <c r="B119">
-        <v>1.611454303438012</v>
+        <v>1.378746350589847</v>
       </c>
       <c r="C119">
-        <v>0.3621417696960933</v>
+        <v>0.387025630936652</v>
       </c>
       <c r="D119">
-        <v>1.317542203797948</v>
+        <v>0.8298536815433254</v>
       </c>
       <c r="E119">
-        <v>0.187656944177393</v>
+        <v>0.4066215155200467</v>
       </c>
       <c r="F119">
-        <v>0.7924326503961633</v>
+        <v>0.6457249414864442</v>
       </c>
       <c r="G119">
-        <v>3.27697877008307</v>
+        <v>2.943887369270416</v>
       </c>
       <c r="H119" t="inlineStr">
         <is>
@@ -7833,7 +7833,7 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_sp + iqr_t1_K_sp + iqr_t2_K_sp + iqr_t3_K_sp</t>
+          <t>pct1_K_sp + t1_K_sp + t2_K_sp + t3_K_sp</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
@@ -7862,32 +7862,32 @@
         </is>
       </c>
       <c r="O119">
-        <v>15307</v>
+        <v>15241</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_sp + iqr_t1_K_sp + iqr_t2_K_sp + iqr_t3_K_sp</t>
+          <t>t2_K_sp</t>
         </is>
       </c>
       <c r="B120">
-        <v>0.4533575859452427</v>
+        <v>0.614063216094957</v>
       </c>
       <c r="C120">
-        <v>0.3802879251336195</v>
+        <v>0.3858838880355658</v>
       </c>
       <c r="D120">
-        <v>-2.080197765060669</v>
+        <v>-1.26374127929504</v>
       </c>
       <c r="E120">
-        <v>0.03750739716326076</v>
+        <v>0.2063229036948173</v>
       </c>
       <c r="F120">
-        <v>0.2151489437747993</v>
+        <v>0.2882359333810692</v>
       </c>
       <c r="G120">
-        <v>0.9553061108644519</v>
+        <v>1.308211744933143</v>
       </c>
       <c r="H120" t="inlineStr">
         <is>
@@ -7896,7 +7896,7 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_sp + iqr_t1_K_sp + iqr_t2_K_sp + iqr_t3_K_sp</t>
+          <t>pct1_K_sp + t1_K_sp + t2_K_sp + t3_K_sp</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
@@ -7925,32 +7925,32 @@
         </is>
       </c>
       <c r="O120">
-        <v>15307</v>
+        <v>15241</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_sp + iqr_t1_K_sp + iqr_t2_K_sp + iqr_t3_K_sp</t>
+          <t>t3_K_sp</t>
         </is>
       </c>
       <c r="B121">
-        <v>1.729027916782697</v>
+        <v>1.649738726429729</v>
       </c>
       <c r="C121">
-        <v>0.2887437221311804</v>
+        <v>0.3576793208091384</v>
       </c>
       <c r="D121">
-        <v>1.896350676409569</v>
+        <v>1.399625023396224</v>
       </c>
       <c r="E121">
-        <v>0.05791368939020002</v>
+        <v>0.1616256365370969</v>
       </c>
       <c r="F121">
-        <v>0.981799719196906</v>
+        <v>0.8183856006241125</v>
       </c>
       <c r="G121">
-        <v>3.044956602207323</v>
+        <v>3.325617976912626</v>
       </c>
       <c r="H121" t="inlineStr">
         <is>
@@ -7959,7 +7959,7 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_sp + iqr_t1_K_sp + iqr_t2_K_sp + iqr_t3_K_sp</t>
+          <t>pct1_K_sp + t1_K_sp + t2_K_sp + t3_K_sp</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
@@ -7988,43 +7988,43 @@
         </is>
       </c>
       <c r="O121">
-        <v>15307</v>
+        <v>15241</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
+          <t>iqr_t1_PM25_cs</t>
+        </is>
+      </c>
+      <c r="B122">
+        <v>1.114977951613583</v>
+      </c>
+      <c r="C122">
+        <v>0.2950664878780073</v>
+      </c>
+      <c r="D122">
+        <v>0.3688478185430882</v>
+      </c>
+      <c r="E122">
+        <v>0.7122411597550896</v>
+      </c>
+      <c r="F122">
+        <v>0.6253241905124587</v>
+      </c>
+      <c r="G122">
+        <v>1.988050120955065</v>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>malf_card_bin</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
           <t>iqr_t1_PM25_cs + iqr_t2_PM25_cs + iqr_t3_PM25_cs</t>
         </is>
       </c>
-      <c r="B122">
-        <v>1.469199583088963</v>
-      </c>
-      <c r="C122">
-        <v>0.3025441562095649</v>
-      </c>
-      <c r="D122">
-        <v>1.271608600925904</v>
-      </c>
-      <c r="E122">
-        <v>0.2035122192905333</v>
-      </c>
-      <c r="F122">
-        <v>0.8119975965749923</v>
-      </c>
-      <c r="G122">
-        <v>2.658317492629953</v>
-      </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>malf_card_bin</t>
-        </is>
-      </c>
-      <c r="I122" t="inlineStr">
-        <is>
-          <t>iqr_t1_PM25_cs + iqr_t2_PM25_cs + iqr_t3_PM25_cs</t>
-        </is>
-      </c>
       <c r="J122" t="inlineStr">
         <is>
           <t>t1_t2_t3</t>
@@ -8051,43 +8051,43 @@
         </is>
       </c>
       <c r="O122">
-        <v>15313</v>
+        <v>15247</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
+          <t>iqr_t2_PM25_cs</t>
+        </is>
+      </c>
+      <c r="B123">
+        <v>0.9221397820672286</v>
+      </c>
+      <c r="C123">
+        <v>0.1604211896285557</v>
+      </c>
+      <c r="D123">
+        <v>-0.5052852410351095</v>
+      </c>
+      <c r="E123">
+        <v>0.6133585074472174</v>
+      </c>
+      <c r="F123">
+        <v>0.673357953380049</v>
+      </c>
+      <c r="G123">
+        <v>1.262837653290561</v>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>malf_card_bin</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
           <t>iqr_t1_PM25_cs + iqr_t2_PM25_cs + iqr_t3_PM25_cs</t>
         </is>
       </c>
-      <c r="B123">
-        <v>0.7617991301901734</v>
-      </c>
-      <c r="C123">
-        <v>0.1837822592396924</v>
-      </c>
-      <c r="D123">
-        <v>-1.480406040529928</v>
-      </c>
-      <c r="E123">
-        <v>0.1387649189390774</v>
-      </c>
-      <c r="F123">
-        <v>0.5313794191854408</v>
-      </c>
-      <c r="G123">
-        <v>1.092134722959562</v>
-      </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>malf_card_bin</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr">
-        <is>
-          <t>iqr_t1_PM25_cs + iqr_t2_PM25_cs + iqr_t3_PM25_cs</t>
-        </is>
-      </c>
       <c r="J123" t="inlineStr">
         <is>
           <t>t1_t2_t3</t>
@@ -8114,43 +8114,43 @@
         </is>
       </c>
       <c r="O123">
-        <v>15313</v>
+        <v>15247</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
+          <t>iqr_t3_PM25_cs</t>
+        </is>
+      </c>
+      <c r="B124">
+        <v>1.317131316441392</v>
+      </c>
+      <c r="C124">
+        <v>0.2876068398095195</v>
+      </c>
+      <c r="D124">
+        <v>0.957752349479534</v>
+      </c>
+      <c r="E124">
+        <v>0.3381876523651203</v>
+      </c>
+      <c r="F124">
+        <v>0.7495794813884573</v>
+      </c>
+      <c r="G124">
+        <v>2.31441087679878</v>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>malf_card_bin</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
           <t>iqr_t1_PM25_cs + iqr_t2_PM25_cs + iqr_t3_PM25_cs</t>
         </is>
       </c>
-      <c r="B124">
-        <v>1.769767923195632</v>
-      </c>
-      <c r="C124">
-        <v>0.2929746093028063</v>
-      </c>
-      <c r="D124">
-        <v>1.948456975534501</v>
-      </c>
-      <c r="E124">
-        <v>0.05136030811327186</v>
-      </c>
-      <c r="F124">
-        <v>0.9966344148537165</v>
-      </c>
-      <c r="G124">
-        <v>3.142655376226297</v>
-      </c>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>malf_card_bin</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr">
-        <is>
-          <t>iqr_t1_PM25_cs + iqr_t2_PM25_cs + iqr_t3_PM25_cs</t>
-        </is>
-      </c>
       <c r="J124" t="inlineStr">
         <is>
           <t>t1_t2_t3</t>
@@ -8177,32 +8177,32 @@
         </is>
       </c>
       <c r="O124">
-        <v>15313</v>
+        <v>15247</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_cs + iqr_t2_Levo_cs + iqr_t3_Levo_cs</t>
+          <t>t1_Levo_cs</t>
         </is>
       </c>
       <c r="B125">
-        <v>1.504778056313683</v>
+        <v>1.175786423933481</v>
       </c>
       <c r="C125">
-        <v>0.3615297311863663</v>
+        <v>0.5462907385486202</v>
       </c>
       <c r="D125">
-        <v>1.130323127497822</v>
+        <v>0.2964304705433878</v>
       </c>
       <c r="E125">
-        <v>0.2583400927467649</v>
+        <v>0.7669013582798272</v>
       </c>
       <c r="F125">
-        <v>0.740862792589421</v>
+        <v>0.4030184437467917</v>
       </c>
       <c r="G125">
-        <v>3.056378348882842</v>
+        <v>3.430298876283844</v>
       </c>
       <c r="H125" t="inlineStr">
         <is>
@@ -8211,7 +8211,7 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_cs + iqr_t2_Levo_cs + iqr_t3_Levo_cs</t>
+          <t>t1_Levo_cs + t2_Levo_cs + t3_Levo_cs</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -8240,32 +8240,32 @@
         </is>
       </c>
       <c r="O125">
-        <v>15313</v>
+        <v>15247</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_cs + iqr_t2_Levo_cs + iqr_t3_Levo_cs</t>
+          <t>t2_Levo_cs</t>
         </is>
       </c>
       <c r="B126">
-        <v>0.7546764313050793</v>
+        <v>0.8678754908409141</v>
       </c>
       <c r="C126">
-        <v>0.1928816212426252</v>
+        <v>0.2600525079811799</v>
       </c>
       <c r="D126">
-        <v>-1.459269097745341</v>
+        <v>-0.5449169455914039</v>
       </c>
       <c r="E126">
-        <v>0.1444910572479891</v>
+        <v>0.5858106410605556</v>
       </c>
       <c r="F126">
-        <v>0.5171060910924282</v>
+        <v>0.5213151278936148</v>
       </c>
       <c r="G126">
-        <v>1.101392007903404</v>
+        <v>1.444822579090905</v>
       </c>
       <c r="H126" t="inlineStr">
         <is>
@@ -8274,7 +8274,7 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_cs + iqr_t2_Levo_cs + iqr_t3_Levo_cs</t>
+          <t>t1_Levo_cs + t2_Levo_cs + t3_Levo_cs</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -8303,32 +8303,32 @@
         </is>
       </c>
       <c r="O126">
-        <v>15313</v>
+        <v>15247</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_cs + iqr_t2_Levo_cs + iqr_t3_Levo_cs</t>
+          <t>t3_Levo_cs</t>
         </is>
       </c>
       <c r="B127">
-        <v>1.785605186048535</v>
+        <v>1.480882343798579</v>
       </c>
       <c r="C127">
-        <v>0.3471446702818428</v>
+        <v>0.538399506162528</v>
       </c>
       <c r="D127">
-        <v>1.670074315423014</v>
+        <v>0.72926903513194</v>
       </c>
       <c r="E127">
-        <v>0.09490466114185528</v>
+        <v>0.4658371095908527</v>
       </c>
       <c r="F127">
-        <v>0.9042642461606063</v>
+        <v>0.515506403852484</v>
       </c>
       <c r="G127">
-        <v>3.525944870629259</v>
+        <v>4.254093644202175</v>
       </c>
       <c r="H127" t="inlineStr">
         <is>
@@ -8337,7 +8337,7 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_cs + iqr_t2_Levo_cs + iqr_t3_Levo_cs</t>
+          <t>t1_Levo_cs + t2_Levo_cs + t3_Levo_cs</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -8366,32 +8366,32 @@
         </is>
       </c>
       <c r="O127">
-        <v>15313</v>
+        <v>15247</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>iqr_t1_K_cs + iqr_t2_K_cs + iqr_t3_K_cs</t>
+          <t>t1_K_cs</t>
         </is>
       </c>
       <c r="B128">
-        <v>1.475764626829052</v>
+        <v>1.145430943514946</v>
       </c>
       <c r="C128">
-        <v>0.3098879315975701</v>
+        <v>0.4563379567166976</v>
       </c>
       <c r="D128">
-        <v>1.255861254543755</v>
+        <v>0.2975446904653805</v>
       </c>
       <c r="E128">
-        <v>0.209166278320268</v>
+        <v>0.7660506939521339</v>
       </c>
       <c r="F128">
-        <v>0.8039703097708381</v>
+        <v>0.468309899464703</v>
       </c>
       <c r="G128">
-        <v>2.708907539658611</v>
+        <v>2.801589391685337</v>
       </c>
       <c r="H128" t="inlineStr">
         <is>
@@ -8400,7 +8400,7 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>iqr_t1_K_cs + iqr_t2_K_cs + iqr_t3_K_cs</t>
+          <t>t1_K_cs + t2_K_cs + t3_K_cs</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -8429,32 +8429,32 @@
         </is>
       </c>
       <c r="O128">
-        <v>15313</v>
+        <v>15247</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>iqr_t1_K_cs + iqr_t2_K_cs + iqr_t3_K_cs</t>
+          <t>t2_K_cs</t>
         </is>
       </c>
       <c r="B129">
-        <v>0.7552616655934749</v>
+        <v>0.8766270718525033</v>
       </c>
       <c r="C129">
-        <v>0.1816589696102135</v>
+        <v>0.240754816372819</v>
       </c>
       <c r="D129">
-        <v>-1.545153610825323</v>
+        <v>-0.5469199356816637</v>
       </c>
       <c r="E129">
-        <v>0.1223091120294259</v>
+        <v>0.584433738896273</v>
       </c>
       <c r="F129">
-        <v>0.5290162915396529</v>
+        <v>0.5468698834555871</v>
       </c>
       <c r="G129">
-        <v>1.078265816455056</v>
+        <v>1.405224618055063</v>
       </c>
       <c r="H129" t="inlineStr">
         <is>
@@ -8463,7 +8463,7 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>iqr_t1_K_cs + iqr_t2_K_cs + iqr_t3_K_cs</t>
+          <t>t1_K_cs + t2_K_cs + t3_K_cs</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -8492,32 +8492,32 @@
         </is>
       </c>
       <c r="O129">
-        <v>15313</v>
+        <v>15247</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>iqr_t1_K_cs + iqr_t2_K_cs + iqr_t3_K_cs</t>
+          <t>t3_K_cs</t>
         </is>
       </c>
       <c r="B130">
-        <v>1.776454846036413</v>
+        <v>1.465146779654824</v>
       </c>
       <c r="C130">
-        <v>0.2977185809755242</v>
+        <v>0.4517398828833381</v>
       </c>
       <c r="D130">
-        <v>1.930076775523471</v>
+        <v>0.8455207140511952</v>
       </c>
       <c r="E130">
-        <v>0.0535973255992146</v>
+        <v>0.397820172371294</v>
       </c>
       <c r="F130">
-        <v>0.991141492389659</v>
+        <v>0.6044487021525714</v>
       </c>
       <c r="G130">
-        <v>3.183997284179465</v>
+        <v>3.551426412676877</v>
       </c>
       <c r="H130" t="inlineStr">
         <is>
@@ -8526,7 +8526,7 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>iqr_t1_K_cs + iqr_t2_K_cs + iqr_t3_K_cs</t>
+          <t>t1_K_cs + t2_K_cs + t3_K_cs</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
@@ -8555,43 +8555,43 @@
         </is>
       </c>
       <c r="O130">
-        <v>15313</v>
+        <v>15247</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
+          <t>iqr_t1_PM25_sp</t>
+        </is>
+      </c>
+      <c r="B131">
+        <v>0.8997972944947686</v>
+      </c>
+      <c r="C131">
+        <v>0.1872801342846528</v>
+      </c>
+      <c r="D131">
+        <v>-0.5637852074806862</v>
+      </c>
+      <c r="E131">
+        <v>0.5729003201836842</v>
+      </c>
+      <c r="F131">
+        <v>0.6233493969769404</v>
+      </c>
+      <c r="G131">
+        <v>1.298846481775062</v>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>malf_card_bin</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
           <t>iqr_t1_PM25_sp + iqr_t2_PM25_sp + iqr_t3_PM25_sp</t>
         </is>
       </c>
-      <c r="B131">
-        <v>1.022474457802604</v>
-      </c>
-      <c r="C131">
-        <v>0.1992983706577195</v>
-      </c>
-      <c r="D131">
-        <v>0.111519368699853</v>
-      </c>
-      <c r="E131">
-        <v>0.9112045073964976</v>
-      </c>
-      <c r="F131">
-        <v>0.6918459247932505</v>
-      </c>
-      <c r="G131">
-        <v>1.511108151964832</v>
-      </c>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>malf_card_bin</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr">
-        <is>
-          <t>iqr_t1_PM25_sp + iqr_t2_PM25_sp + iqr_t3_PM25_sp</t>
-        </is>
-      </c>
       <c r="J131" t="inlineStr">
         <is>
           <t>t1_t2_t3</t>
@@ -8618,43 +8618,43 @@
         </is>
       </c>
       <c r="O131">
-        <v>15313</v>
+        <v>15247</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
+          <t>iqr_t2_PM25_sp</t>
+        </is>
+      </c>
+      <c r="B132">
+        <v>0.8847224657545608</v>
+      </c>
+      <c r="C132">
+        <v>0.1512080284636662</v>
+      </c>
+      <c r="D132">
+        <v>-0.8100183728222128</v>
+      </c>
+      <c r="E132">
+        <v>0.417929616266469</v>
+      </c>
+      <c r="F132">
+        <v>0.6578070872354321</v>
+      </c>
+      <c r="G132">
+        <v>1.189913968091204</v>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>malf_card_bin</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
           <t>iqr_t1_PM25_sp + iqr_t2_PM25_sp + iqr_t3_PM25_sp</t>
         </is>
       </c>
-      <c r="B132">
-        <v>0.7927547202678409</v>
-      </c>
-      <c r="C132">
-        <v>0.1703963531154614</v>
-      </c>
-      <c r="D132">
-        <v>-1.362948250004119</v>
-      </c>
-      <c r="E132">
-        <v>0.1728988206991332</v>
-      </c>
-      <c r="F132">
-        <v>0.5676716397314219</v>
-      </c>
-      <c r="G132">
-        <v>1.107083747929139</v>
-      </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>malf_card_bin</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t>iqr_t1_PM25_sp + iqr_t2_PM25_sp + iqr_t3_PM25_sp</t>
-        </is>
-      </c>
       <c r="J132" t="inlineStr">
         <is>
           <t>t1_t2_t3</t>
@@ -8681,43 +8681,43 @@
         </is>
       </c>
       <c r="O132">
-        <v>15313</v>
+        <v>15247</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
+          <t>iqr_t3_PM25_sp</t>
+        </is>
+      </c>
+      <c r="B133">
+        <v>1.03326556237535</v>
+      </c>
+      <c r="C133">
+        <v>0.1788200841620296</v>
+      </c>
+      <c r="D133">
+        <v>0.1830008973964814</v>
+      </c>
+      <c r="E133">
+        <v>0.8547973144881971</v>
+      </c>
+      <c r="F133">
+        <v>0.7277798438641133</v>
+      </c>
+      <c r="G133">
+        <v>1.466978965400135</v>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>malf_card_bin</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
           <t>iqr_t1_PM25_sp + iqr_t2_PM25_sp + iqr_t3_PM25_sp</t>
         </is>
       </c>
-      <c r="B133">
-        <v>1.196485801410298</v>
-      </c>
-      <c r="C133">
-        <v>0.1892425727393948</v>
-      </c>
-      <c r="D133">
-        <v>0.9479302618307774</v>
-      </c>
-      <c r="E133">
-        <v>0.3431649579209621</v>
-      </c>
-      <c r="F133">
-        <v>0.8257032220315428</v>
-      </c>
-      <c r="G133">
-        <v>1.733768543925768</v>
-      </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>malf_card_bin</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr">
-        <is>
-          <t>iqr_t1_PM25_sp + iqr_t2_PM25_sp + iqr_t3_PM25_sp</t>
-        </is>
-      </c>
       <c r="J133" t="inlineStr">
         <is>
           <t>t1_t2_t3</t>
@@ -8744,32 +8744,32 @@
         </is>
       </c>
       <c r="O133">
-        <v>15313</v>
+        <v>15247</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_sp + iqr_t2_Levo_sp + iqr_t3_Levo_sp</t>
+          <t>t1_Levo_sp</t>
         </is>
       </c>
       <c r="B134">
-        <v>1.313905874470176</v>
+        <v>1.076381541376842</v>
       </c>
       <c r="C134">
-        <v>0.2969551799295085</v>
+        <v>0.4194457180835439</v>
       </c>
       <c r="D134">
-        <v>0.9193450834505242</v>
+        <v>0.1754815654825214</v>
       </c>
       <c r="E134">
-        <v>0.3579151037748667</v>
+        <v>0.8607012546406023</v>
       </c>
       <c r="F134">
-        <v>0.7341681620400177</v>
+        <v>0.4730787046757005</v>
       </c>
       <c r="G134">
-        <v>2.351434911274644</v>
+        <v>2.449058076733797</v>
       </c>
       <c r="H134" t="inlineStr">
         <is>
@@ -8778,7 +8778,7 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_sp + iqr_t2_Levo_sp + iqr_t3_Levo_sp</t>
+          <t>t1_Levo_sp + t2_Levo_sp + t3_Levo_sp</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -8807,32 +8807,32 @@
         </is>
       </c>
       <c r="O134">
-        <v>15313</v>
+        <v>15247</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_sp + iqr_t2_Levo_sp + iqr_t3_Levo_sp</t>
+          <t>t2_Levo_sp</t>
         </is>
       </c>
       <c r="B135">
-        <v>0.7601005339461174</v>
+        <v>0.8449861724679373</v>
       </c>
       <c r="C135">
-        <v>0.1844687369740719</v>
+        <v>0.2388224392578273</v>
       </c>
       <c r="D135">
-        <v>-1.486997620527392</v>
+        <v>-0.7052729895296183</v>
       </c>
       <c r="E135">
-        <v>0.1370154393991957</v>
+        <v>0.4806403661783425</v>
       </c>
       <c r="F135">
-        <v>0.5294817115212689</v>
+        <v>0.5291314473181824</v>
       </c>
       <c r="G135">
-        <v>1.091166718573177</v>
+        <v>1.349384231991534</v>
       </c>
       <c r="H135" t="inlineStr">
         <is>
@@ -8841,7 +8841,7 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_sp + iqr_t2_Levo_sp + iqr_t3_Levo_sp</t>
+          <t>t1_Levo_sp + t2_Levo_sp + t3_Levo_sp</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -8870,32 +8870,32 @@
         </is>
       </c>
       <c r="O135">
-        <v>15313</v>
+        <v>15247</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_sp + iqr_t2_Levo_sp + iqr_t3_Levo_sp</t>
+          <t>t3_Levo_sp</t>
         </is>
       </c>
       <c r="B136">
-        <v>1.525127319318742</v>
+        <v>1.306339375925263</v>
       </c>
       <c r="C136">
-        <v>0.2868372001824847</v>
+        <v>0.4138201341988996</v>
       </c>
       <c r="D136">
-        <v>1.471489382771059</v>
+        <v>0.6457608851454476</v>
       </c>
       <c r="E136">
-        <v>0.1411588167317132</v>
+        <v>0.518434223214559</v>
       </c>
       <c r="F136">
-        <v>0.8692602754323804</v>
+        <v>0.5805126404601669</v>
       </c>
       <c r="G136">
-        <v>2.675853718238058</v>
+        <v>2.939682008887976</v>
       </c>
       <c r="H136" t="inlineStr">
         <is>
@@ -8904,7 +8904,7 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_sp + iqr_t2_Levo_sp + iqr_t3_Levo_sp</t>
+          <t>t1_Levo_sp + t2_Levo_sp + t3_Levo_sp</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -8933,32 +8933,32 @@
         </is>
       </c>
       <c r="O136">
-        <v>15313</v>
+        <v>15247</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>iqr_t1_K_sp + iqr_t2_K_sp + iqr_t3_K_sp</t>
+          <t>t1_K_sp</t>
         </is>
       </c>
       <c r="B137">
-        <v>1.081907339667413</v>
+        <v>0.913377858846306</v>
       </c>
       <c r="C137">
-        <v>0.2235324140675431</v>
+        <v>0.2285243995997608</v>
       </c>
       <c r="D137">
-        <v>0.3521884692661532</v>
+        <v>-0.3964811593573349</v>
       </c>
       <c r="E137">
-        <v>0.7246969238765057</v>
+        <v>0.6917501041591338</v>
       </c>
       <c r="F137">
-        <v>0.6981020788038219</v>
+        <v>0.5836199890126594</v>
       </c>
       <c r="G137">
-        <v>1.676722541253391</v>
+        <v>1.429456030870399</v>
       </c>
       <c r="H137" t="inlineStr">
         <is>
@@ -8967,7 +8967,7 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>iqr_t1_K_sp + iqr_t2_K_sp + iqr_t3_K_sp</t>
+          <t>t1_K_sp + t2_K_sp + t3_K_sp</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -8996,32 +8996,32 @@
         </is>
       </c>
       <c r="O137">
-        <v>15313</v>
+        <v>15247</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>iqr_t1_K_sp + iqr_t2_K_sp + iqr_t3_K_sp</t>
+          <t>t2_K_sp</t>
         </is>
       </c>
       <c r="B138">
-        <v>0.7645572060666314</v>
+        <v>0.8602065237581404</v>
       </c>
       <c r="C138">
-        <v>0.1709829452822299</v>
+        <v>0.1623060915127195</v>
       </c>
       <c r="D138">
-        <v>-1.570088922553455</v>
+        <v>-0.9277703212260552</v>
       </c>
       <c r="E138">
-        <v>0.116394425328724</v>
+        <v>0.3535267222053681</v>
       </c>
       <c r="F138">
-        <v>0.5468510358136036</v>
+        <v>0.6258172593334383</v>
       </c>
       <c r="G138">
-        <v>1.068934102828798</v>
+        <v>1.182382320845857</v>
       </c>
       <c r="H138" t="inlineStr">
         <is>
@@ -9030,7 +9030,7 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>iqr_t1_K_sp + iqr_t2_K_sp + iqr_t3_K_sp</t>
+          <t>t1_K_sp + t2_K_sp + t3_K_sp</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -9059,32 +9059,32 @@
         </is>
       </c>
       <c r="O138">
-        <v>15313</v>
+        <v>15247</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>iqr_t1_K_sp + iqr_t2_K_sp + iqr_t3_K_sp</t>
+          <t>t3_K_sp</t>
         </is>
       </c>
       <c r="B139">
-        <v>1.274986422209002</v>
+        <v>1.072565814358023</v>
       </c>
       <c r="C139">
-        <v>0.2092586844837748</v>
+        <v>0.2232666298692021</v>
       </c>
       <c r="D139">
-        <v>1.160934036764818</v>
+        <v>0.3137671552040001</v>
       </c>
       <c r="E139">
-        <v>0.2456687257785102</v>
+        <v>0.7536978918424706</v>
       </c>
       <c r="F139">
-        <v>0.8460270416727369</v>
+        <v>0.6924350622877793</v>
       </c>
       <c r="G139">
-        <v>1.921440210236362</v>
+        <v>1.661379512367008</v>
       </c>
       <c r="H139" t="inlineStr">
         <is>
@@ -9093,7 +9093,7 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>iqr_t1_K_sp + iqr_t2_K_sp + iqr_t3_K_sp</t>
+          <t>t1_K_sp + t2_K_sp + t3_K_sp</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -9122,43 +9122,43 @@
         </is>
       </c>
       <c r="O139">
-        <v>15313</v>
+        <v>15247</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
+          <t>iqr_t1_PM25_cs</t>
+        </is>
+      </c>
+      <c r="B140">
+        <v>1.742671792111266</v>
+      </c>
+      <c r="C140">
+        <v>0.5421013345742545</v>
+      </c>
+      <c r="D140">
+        <v>1.024567572179196</v>
+      </c>
+      <c r="E140">
+        <v>0.3055672719711147</v>
+      </c>
+      <c r="F140">
+        <v>0.6022518031333972</v>
+      </c>
+      <c r="G140">
+        <v>5.042583449679807</v>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>malf_card_bin</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
           <t>iqr_t1_PM25_cs + iqr_t2_PM25_cs + iqr_t3_PM25_cs</t>
         </is>
       </c>
-      <c r="B140">
-        <v>2.001039083046212</v>
-      </c>
-      <c r="C140">
-        <v>0.4865528760205159</v>
-      </c>
-      <c r="D140">
-        <v>1.425675648742507</v>
-      </c>
-      <c r="E140">
-        <v>0.1539619887348008</v>
-      </c>
-      <c r="F140">
-        <v>0.7710827936635516</v>
-      </c>
-      <c r="G140">
-        <v>5.19290203955137</v>
-      </c>
-      <c r="H140" t="inlineStr">
-        <is>
-          <t>malf_card_bin</t>
-        </is>
-      </c>
-      <c r="I140" t="inlineStr">
-        <is>
-          <t>iqr_t1_PM25_cs + iqr_t2_PM25_cs + iqr_t3_PM25_cs</t>
-        </is>
-      </c>
       <c r="J140" t="inlineStr">
         <is>
           <t>t1_t2_t3</t>
@@ -9185,43 +9185,43 @@
         </is>
       </c>
       <c r="O140">
-        <v>15313</v>
+        <v>15247</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
+          <t>iqr_t2_PM25_cs</t>
+        </is>
+      </c>
+      <c r="B141">
+        <v>1.573400951679167</v>
+      </c>
+      <c r="C141">
+        <v>0.391136409800184</v>
+      </c>
+      <c r="D141">
+        <v>1.158776008604163</v>
+      </c>
+      <c r="E141">
+        <v>0.2465474991795475</v>
+      </c>
+      <c r="F141">
+        <v>0.7309766308515929</v>
+      </c>
+      <c r="G141">
+        <v>3.386689054424119</v>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>malf_card_bin</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
           <t>iqr_t1_PM25_cs + iqr_t2_PM25_cs + iqr_t3_PM25_cs</t>
         </is>
       </c>
-      <c r="B141">
-        <v>0.9855045671852137</v>
-      </c>
-      <c r="C141">
-        <v>0.3883870115145389</v>
-      </c>
-      <c r="D141">
-        <v>-0.0375952788930374</v>
-      </c>
-      <c r="E141">
-        <v>0.970010372160156</v>
-      </c>
-      <c r="F141">
-        <v>0.4603233633546084</v>
-      </c>
-      <c r="G141">
-        <v>2.109863042503755</v>
-      </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>malf_card_bin</t>
-        </is>
-      </c>
-      <c r="I141" t="inlineStr">
-        <is>
-          <t>iqr_t1_PM25_cs + iqr_t2_PM25_cs + iqr_t3_PM25_cs</t>
-        </is>
-      </c>
       <c r="J141" t="inlineStr">
         <is>
           <t>t1_t2_t3</t>
@@ -9248,43 +9248,43 @@
         </is>
       </c>
       <c r="O141">
-        <v>15313</v>
+        <v>15247</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
+          <t>iqr_t3_PM25_cs</t>
+        </is>
+      </c>
+      <c r="B142">
+        <v>2.421122667876844</v>
+      </c>
+      <c r="C142">
+        <v>0.5241668387533841</v>
+      </c>
+      <c r="D142">
+        <v>1.686927290256066</v>
+      </c>
+      <c r="E142">
+        <v>0.09161733381923155</v>
+      </c>
+      <c r="F142">
+        <v>0.8666528544796711</v>
+      </c>
+      <c r="G142">
+        <v>6.763763533008226</v>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>malf_card_bin</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
           <t>iqr_t1_PM25_cs + iqr_t2_PM25_cs + iqr_t3_PM25_cs</t>
         </is>
       </c>
-      <c r="B142">
-        <v>3.301731767956483</v>
-      </c>
-      <c r="C142">
-        <v>0.4646517731940682</v>
-      </c>
-      <c r="D142">
-        <v>2.570628539265855</v>
-      </c>
-      <c r="E142">
-        <v>0.0101514146822811</v>
-      </c>
-      <c r="F142">
-        <v>1.328096040615801</v>
-      </c>
-      <c r="G142">
-        <v>8.208316517891545</v>
-      </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>malf_card_bin</t>
-        </is>
-      </c>
-      <c r="I142" t="inlineStr">
-        <is>
-          <t>iqr_t1_PM25_cs + iqr_t2_PM25_cs + iqr_t3_PM25_cs</t>
-        </is>
-      </c>
       <c r="J142" t="inlineStr">
         <is>
           <t>t1_t2_t3</t>
@@ -9311,32 +9311,32 @@
         </is>
       </c>
       <c r="O142">
-        <v>15313</v>
+        <v>15247</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_cs + iqr_t2_Levo_cs + iqr_t3_Levo_cs</t>
+          <t>t1_Levo_cs</t>
         </is>
       </c>
       <c r="B143">
-        <v>1.97176162421846</v>
+        <v>2.339487301803397</v>
       </c>
       <c r="C143">
-        <v>0.5336363727720133</v>
+        <v>0.8717978747289982</v>
       </c>
       <c r="D143">
-        <v>1.272265916083158</v>
+        <v>0.9749184165355876</v>
       </c>
       <c r="E143">
-        <v>0.2032786543728404</v>
+        <v>0.3296007300237132</v>
       </c>
       <c r="F143">
-        <v>0.6928230144502077</v>
+        <v>0.4236868606956344</v>
       </c>
       <c r="G143">
-        <v>5.611597509972777</v>
+        <v>12.91803296971049</v>
       </c>
       <c r="H143" t="inlineStr">
         <is>
@@ -9345,7 +9345,7 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_cs + iqr_t2_Levo_cs + iqr_t3_Levo_cs</t>
+          <t>t1_Levo_cs + t2_Levo_cs + t3_Levo_cs</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
@@ -9374,32 +9374,32 @@
         </is>
       </c>
       <c r="O143">
-        <v>15313</v>
+        <v>15247</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_cs + iqr_t2_Levo_cs + iqr_t3_Levo_cs</t>
+          <t>t2_Levo_cs</t>
         </is>
       </c>
       <c r="B144">
-        <v>0.9033000420455269</v>
+        <v>1.875457947555423</v>
       </c>
       <c r="C144">
-        <v>0.4263311320837855</v>
+        <v>0.620609017240157</v>
       </c>
       <c r="D144">
-        <v>-0.2385481627454129</v>
+        <v>1.013283485782544</v>
       </c>
       <c r="E144">
-        <v>0.8114559648036692</v>
+        <v>0.3109247732277535</v>
       </c>
       <c r="F144">
-        <v>0.3916862381200695</v>
+        <v>0.55570458161087</v>
       </c>
       <c r="G144">
-        <v>2.083174966462122</v>
+        <v>6.329518649734306</v>
       </c>
       <c r="H144" t="inlineStr">
         <is>
@@ -9408,7 +9408,7 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_cs + iqr_t2_Levo_cs + iqr_t3_Levo_cs</t>
+          <t>t1_Levo_cs + t2_Levo_cs + t3_Levo_cs</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
@@ -9437,32 +9437,32 @@
         </is>
       </c>
       <c r="O144">
-        <v>15313</v>
+        <v>15247</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_cs + iqr_t2_Levo_cs + iqr_t3_Levo_cs</t>
+          <t>t3_Levo_cs</t>
         </is>
       </c>
       <c r="B145">
-        <v>3.226827498017169</v>
+        <v>3.750682835705932</v>
       </c>
       <c r="C145">
-        <v>0.5010354457396479</v>
+        <v>0.8515531271061568</v>
       </c>
       <c r="D145">
-        <v>2.338156842527537</v>
+        <v>1.552384544015444</v>
       </c>
       <c r="E145">
-        <v>0.0193791133893186</v>
+        <v>0.1205702394389567</v>
       </c>
       <c r="F145">
-        <v>1.208630653182297</v>
+        <v>0.7067519331656908</v>
       </c>
       <c r="G145">
-        <v>8.615051814666531</v>
+        <v>19.90461019476417</v>
       </c>
       <c r="H145" t="inlineStr">
         <is>
@@ -9471,7 +9471,7 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_cs + iqr_t2_Levo_cs + iqr_t3_Levo_cs</t>
+          <t>t1_Levo_cs + t2_Levo_cs + t3_Levo_cs</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
@@ -9500,32 +9500,32 @@
         </is>
       </c>
       <c r="O145">
-        <v>15313</v>
+        <v>15247</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>iqr_t1_K_cs + iqr_t2_K_cs + iqr_t3_K_cs</t>
+          <t>t1_K_cs</t>
         </is>
       </c>
       <c r="B146">
-        <v>1.971467462557101</v>
+        <v>2.253740683386605</v>
       </c>
       <c r="C146">
-        <v>0.4663487413255232</v>
+        <v>0.7614802478542654</v>
       </c>
       <c r="D146">
-        <v>1.45551624813649</v>
+        <v>1.067120734896606</v>
       </c>
       <c r="E146">
-        <v>0.1455263953608645</v>
+        <v>0.2859173197939567</v>
       </c>
       <c r="F146">
-        <v>0.7903743642755993</v>
+        <v>0.5066765238492728</v>
       </c>
       <c r="G146">
-        <v>4.91752279881141</v>
+        <v>10.02483207503597</v>
       </c>
       <c r="H146" t="inlineStr">
         <is>
@@ -9534,7 +9534,7 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>iqr_t1_K_cs + iqr_t2_K_cs + iqr_t3_K_cs</t>
+          <t>t1_K_cs + t2_K_cs + t3_K_cs</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
@@ -9563,32 +9563,32 @@
         </is>
       </c>
       <c r="O146">
-        <v>15313</v>
+        <v>15247</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>iqr_t1_K_cs + iqr_t2_K_cs + iqr_t3_K_cs</t>
+          <t>t2_K_cs</t>
         </is>
       </c>
       <c r="B147">
-        <v>0.9081649785944702</v>
+        <v>1.800699516269935</v>
       </c>
       <c r="C147">
-        <v>0.3860332557448937</v>
+        <v>0.567137318444996</v>
       </c>
       <c r="D147">
-        <v>-0.2495360722539517</v>
+        <v>1.037094880604079</v>
       </c>
       <c r="E147">
-        <v>0.8029461415634238</v>
+        <v>0.2996916408245485</v>
       </c>
       <c r="F147">
-        <v>0.4261599641517104</v>
+        <v>0.5925064565615169</v>
       </c>
       <c r="G147">
-        <v>1.93533813057081</v>
+        <v>5.472545846524669</v>
       </c>
       <c r="H147" t="inlineStr">
         <is>
@@ -9597,7 +9597,7 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>iqr_t1_K_cs + iqr_t2_K_cs + iqr_t3_K_cs</t>
+          <t>t1_K_cs + t2_K_cs + t3_K_cs</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
@@ -9626,32 +9626,32 @@
         </is>
       </c>
       <c r="O147">
-        <v>15313</v>
+        <v>15247</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>iqr_t1_K_cs + iqr_t2_K_cs + iqr_t3_K_cs</t>
+          <t>t3_K_cs</t>
         </is>
       </c>
       <c r="B148">
-        <v>3.236765813471724</v>
+        <v>3.633190557301181</v>
       </c>
       <c r="C148">
-        <v>0.4356881515867564</v>
+        <v>0.7413447121046549</v>
       </c>
       <c r="D148">
-        <v>2.695906742629488</v>
+        <v>1.740231207661345</v>
       </c>
       <c r="E148">
-        <v>0.00701973166442591</v>
+        <v>0.08181842787492349</v>
       </c>
       <c r="F148">
-        <v>1.378011530262297</v>
+        <v>0.8496780786664592</v>
       </c>
       <c r="G148">
-        <v>7.602732416371798</v>
+        <v>15.53538211363477</v>
       </c>
       <c r="H148" t="inlineStr">
         <is>
@@ -9660,7 +9660,7 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>iqr_t1_K_cs + iqr_t2_K_cs + iqr_t3_K_cs</t>
+          <t>t1_K_cs + t2_K_cs + t3_K_cs</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
@@ -9689,43 +9689,43 @@
         </is>
       </c>
       <c r="O148">
-        <v>15313</v>
+        <v>15247</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
+          <t>iqr_t1_PM25_sp</t>
+        </is>
+      </c>
+      <c r="B149">
+        <v>0.8317816860356803</v>
+      </c>
+      <c r="C149">
+        <v>0.2817932933577932</v>
+      </c>
+      <c r="D149">
+        <v>-0.6536183561714785</v>
+      </c>
+      <c r="E149">
+        <v>0.5133577150231015</v>
+      </c>
+      <c r="F149">
+        <v>0.478791539701464</v>
+      </c>
+      <c r="G149">
+        <v>1.445014616707195</v>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>malf_card_bin</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
           <t>iqr_t1_PM25_sp + iqr_t2_PM25_sp + iqr_t3_PM25_sp</t>
         </is>
       </c>
-      <c r="B149">
-        <v>0.9680747328269899</v>
-      </c>
-      <c r="C149">
-        <v>0.2963066754167732</v>
-      </c>
-      <c r="D149">
-        <v>-0.1095013850304911</v>
-      </c>
-      <c r="E149">
-        <v>0.9128048232808259</v>
-      </c>
-      <c r="F149">
-        <v>0.5416168731806683</v>
-      </c>
-      <c r="G149">
-        <v>1.7303166403116</v>
-      </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>malf_card_bin</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr">
-        <is>
-          <t>iqr_t1_PM25_sp + iqr_t2_PM25_sp + iqr_t3_PM25_sp</t>
-        </is>
-      </c>
       <c r="J149" t="inlineStr">
         <is>
           <t>t1_t2_t3</t>
@@ -9752,43 +9752,43 @@
         </is>
       </c>
       <c r="O149">
-        <v>15313</v>
+        <v>15247</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
+          <t>iqr_t2_PM25_sp</t>
+        </is>
+      </c>
+      <c r="B150">
+        <v>1.033715941404136</v>
+      </c>
+      <c r="C150">
+        <v>0.2957457274543035</v>
+      </c>
+      <c r="D150">
+        <v>0.1121234124053129</v>
+      </c>
+      <c r="E150">
+        <v>0.9107255540590805</v>
+      </c>
+      <c r="F150">
+        <v>0.5789779099406925</v>
+      </c>
+      <c r="G150">
+        <v>1.845612119506421</v>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>malf_card_bin</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
           <t>iqr_t1_PM25_sp + iqr_t2_PM25_sp + iqr_t3_PM25_sp</t>
         </is>
       </c>
-      <c r="B150">
-        <v>0.7612250366398449</v>
-      </c>
-      <c r="C150">
-        <v>0.3272432545785011</v>
-      </c>
-      <c r="D150">
-        <v>-0.8337108535314626</v>
-      </c>
-      <c r="E150">
-        <v>0.4044439405567964</v>
-      </c>
-      <c r="F150">
-        <v>0.400832659703717</v>
-      </c>
-      <c r="G150">
-        <v>1.445649555691531</v>
-      </c>
-      <c r="H150" t="inlineStr">
-        <is>
-          <t>malf_card_bin</t>
-        </is>
-      </c>
-      <c r="I150" t="inlineStr">
-        <is>
-          <t>iqr_t1_PM25_sp + iqr_t2_PM25_sp + iqr_t3_PM25_sp</t>
-        </is>
-      </c>
       <c r="J150" t="inlineStr">
         <is>
           <t>t1_t2_t3</t>
@@ -9815,43 +9815,43 @@
         </is>
       </c>
       <c r="O150">
-        <v>15313</v>
+        <v>15247</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
+          <t>iqr_t3_PM25_sp</t>
+        </is>
+      </c>
+      <c r="B151">
+        <v>0.9925187411381429</v>
+      </c>
+      <c r="C151">
+        <v>0.2584390717439494</v>
+      </c>
+      <c r="D151">
+        <v>-0.0290566894144955</v>
+      </c>
+      <c r="E151">
+        <v>0.9768193780398735</v>
+      </c>
+      <c r="F151">
+        <v>0.5980740778762083</v>
+      </c>
+      <c r="G151">
+        <v>1.647109426659255</v>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>malf_card_bin</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
           <t>iqr_t1_PM25_sp + iqr_t2_PM25_sp + iqr_t3_PM25_sp</t>
         </is>
       </c>
-      <c r="B151">
-        <v>1.284895304097127</v>
-      </c>
-      <c r="C151">
-        <v>0.2585908339743674</v>
-      </c>
-      <c r="D151">
-        <v>0.9693972356419005</v>
-      </c>
-      <c r="E151">
-        <v>0.3323470310520044</v>
-      </c>
-      <c r="F151">
-        <v>0.7740247093285748</v>
-      </c>
-      <c r="G151">
-        <v>2.132949920840337</v>
-      </c>
-      <c r="H151" t="inlineStr">
-        <is>
-          <t>malf_card_bin</t>
-        </is>
-      </c>
-      <c r="I151" t="inlineStr">
-        <is>
-          <t>iqr_t1_PM25_sp + iqr_t2_PM25_sp + iqr_t3_PM25_sp</t>
-        </is>
-      </c>
       <c r="J151" t="inlineStr">
         <is>
           <t>t1_t2_t3</t>
@@ -9878,32 +9878,32 @@
         </is>
       </c>
       <c r="O151">
-        <v>15313</v>
+        <v>15247</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_sp + iqr_t2_Levo_sp + iqr_t3_Levo_sp</t>
+          <t>t1_Levo_sp</t>
         </is>
       </c>
       <c r="B152">
-        <v>1.435446667835194</v>
+        <v>1.228515117507367</v>
       </c>
       <c r="C152">
-        <v>0.4203791148637782</v>
+        <v>0.5916234656582123</v>
       </c>
       <c r="D152">
-        <v>0.8598811282034577</v>
+        <v>0.347866895944898</v>
       </c>
       <c r="E152">
-        <v>0.3898545723253516</v>
+        <v>0.7279401475818124</v>
       </c>
       <c r="F152">
-        <v>0.6297377239783395</v>
+        <v>0.3852917395716645</v>
       </c>
       <c r="G152">
-        <v>3.272008421509199</v>
+        <v>3.917160008730006</v>
       </c>
       <c r="H152" t="inlineStr">
         <is>
@@ -9912,7 +9912,7 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_sp + iqr_t2_Levo_sp + iqr_t3_Levo_sp</t>
+          <t>t1_Levo_sp + t2_Levo_sp + t3_Levo_sp</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
@@ -9941,32 +9941,32 @@
         </is>
       </c>
       <c r="O152">
-        <v>15313</v>
+        <v>15247</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_sp + iqr_t2_Levo_sp + iqr_t3_Levo_sp</t>
+          <t>t2_Levo_sp</t>
         </is>
       </c>
       <c r="B153">
-        <v>0.759982270500721</v>
+        <v>1.19532807128153</v>
       </c>
       <c r="C153">
-        <v>0.3900090821258062</v>
+        <v>0.5081850542391668</v>
       </c>
       <c r="D153">
-        <v>-0.7037276485111719</v>
+        <v>0.3510939230780314</v>
       </c>
       <c r="E153">
-        <v>0.4816023985845426</v>
+        <v>0.7255178868050958</v>
       </c>
       <c r="F153">
-        <v>0.3538564597987227</v>
+        <v>0.4414883178395142</v>
       </c>
       <c r="G153">
-        <v>1.632224127839748</v>
+        <v>3.236346558354486</v>
       </c>
       <c r="H153" t="inlineStr">
         <is>
@@ -9975,7 +9975,7 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_sp + iqr_t2_Levo_sp + iqr_t3_Levo_sp</t>
+          <t>t1_Levo_sp + t2_Levo_sp + t3_Levo_sp</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
@@ -10004,32 +10004,32 @@
         </is>
       </c>
       <c r="O153">
-        <v>15313</v>
+        <v>15247</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_sp + iqr_t2_Levo_sp + iqr_t3_Levo_sp</t>
+          <t>t3_Levo_sp</t>
         </is>
       </c>
       <c r="B154">
-        <v>1.957745129444288</v>
+        <v>1.622488088298363</v>
       </c>
       <c r="C154">
-        <v>0.3846642577986482</v>
+        <v>0.5655971555142784</v>
       </c>
       <c r="D154">
-        <v>1.746440832992935</v>
+        <v>0.8556634758115986</v>
       </c>
       <c r="E154">
-        <v>0.08073437980735601</v>
+        <v>0.3921839484136864</v>
       </c>
       <c r="F154">
-        <v>0.9211478490490214</v>
+        <v>0.535481344856847</v>
       </c>
       <c r="G154">
-        <v>4.160858645894598</v>
+        <v>4.916077136868002</v>
       </c>
       <c r="H154" t="inlineStr">
         <is>
@@ -10038,7 +10038,7 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_sp + iqr_t2_Levo_sp + iqr_t3_Levo_sp</t>
+          <t>t1_Levo_sp + t2_Levo_sp + t3_Levo_sp</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
@@ -10067,32 +10067,32 @@
         </is>
       </c>
       <c r="O154">
-        <v>15313</v>
+        <v>15247</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>iqr_t1_K_sp + iqr_t2_K_sp + iqr_t3_K_sp</t>
+          <t>t1_K_sp</t>
         </is>
       </c>
       <c r="B155">
-        <v>1.068572290877098</v>
+        <v>0.8793705329645012</v>
       </c>
       <c r="C155">
-        <v>0.3213838355257977</v>
+        <v>0.3305325561280408</v>
       </c>
       <c r="D155">
-        <v>0.2063683439236627</v>
+        <v>-0.3889145820210626</v>
       </c>
       <c r="E155">
-        <v>0.8365031964906144</v>
+        <v>0.6973393348250044</v>
       </c>
       <c r="F155">
-        <v>0.5691693322299214</v>
+        <v>0.4600680633501833</v>
       </c>
       <c r="G155">
-        <v>2.00616350209303</v>
+        <v>1.680822025800289</v>
       </c>
       <c r="H155" t="inlineStr">
         <is>
@@ -10101,7 +10101,7 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>iqr_t1_K_sp + iqr_t2_K_sp + iqr_t3_K_sp</t>
+          <t>t1_K_sp + t2_K_sp + t3_K_sp</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
@@ -10130,32 +10130,32 @@
         </is>
       </c>
       <c r="O155">
-        <v>15313</v>
+        <v>15247</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>iqr_t1_K_sp + iqr_t2_K_sp + iqr_t3_K_sp</t>
+          <t>t2_K_sp</t>
         </is>
       </c>
       <c r="B156">
-        <v>0.6762287026968895</v>
+        <v>0.9550615274820864</v>
       </c>
       <c r="C156">
-        <v>0.3334611107202836</v>
+        <v>0.3207207520388909</v>
       </c>
       <c r="D156">
-        <v>-1.173222093909739</v>
+        <v>-0.1433630770743762</v>
       </c>
       <c r="E156">
-        <v>0.2407067542524471</v>
+        <v>0.8860034419323923</v>
       </c>
       <c r="F156">
-        <v>0.3517636739048821</v>
+        <v>0.5093699867570813</v>
       </c>
       <c r="G156">
-        <v>1.299978628477622</v>
+        <v>1.790726868466668</v>
       </c>
       <c r="H156" t="inlineStr">
         <is>
@@ -10164,7 +10164,7 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>iqr_t1_K_sp + iqr_t2_K_sp + iqr_t3_K_sp</t>
+          <t>t1_K_sp + t2_K_sp + t3_K_sp</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
@@ -10193,32 +10193,32 @@
         </is>
       </c>
       <c r="O156">
-        <v>15313</v>
+        <v>15247</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>iqr_t1_K_sp + iqr_t2_K_sp + iqr_t3_K_sp</t>
+          <t>t3_K_sp</t>
         </is>
       </c>
       <c r="B157">
-        <v>1.456319193694071</v>
+        <v>1.108782723478339</v>
       </c>
       <c r="C157">
-        <v>0.2748466723990172</v>
+        <v>0.3082932003456362</v>
       </c>
       <c r="D157">
-        <v>1.367715857372228</v>
+        <v>0.3349498721924036</v>
       </c>
       <c r="E157">
-        <v>0.171401034371598</v>
+        <v>0.7376629002567037</v>
       </c>
       <c r="F157">
-        <v>0.8497803055309335</v>
+        <v>0.605936065288751</v>
       </c>
       <c r="G157">
-        <v>2.495781062608477</v>
+        <v>2.028925489520397</v>
       </c>
       <c r="H157" t="inlineStr">
         <is>
@@ -10227,7 +10227,7 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>iqr_t1_K_sp + iqr_t2_K_sp + iqr_t3_K_sp</t>
+          <t>t1_K_sp + t2_K_sp + t3_K_sp</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
@@ -10256,7 +10256,7 @@
         </is>
       </c>
       <c r="O157">
-        <v>15313</v>
+        <v>15247</v>
       </c>
     </row>
   </sheetData>
